--- a/links/Juegos_PS3.xlsx
+++ b/links/Juegos_PS3.xlsx
@@ -397,14 +397,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU61"/>
+  <dimension ref="A1:X61"/>
   <cols>
     <col min="1" max="1" width="45.83203125" customWidth="1"/>
     <col min="2" max="2" width="45.83203125" customWidth="1"/>
     <col min="3" max="3" width="45.83203125" customWidth="1"/>
     <col min="4" max="4" width="30.83203125" customWidth="1"/>
-    <col min="5" max="5" width="20.83203125" customWidth="1"/>
-    <col min="6" max="6" width="35.83203125" customWidth="1"/>
+    <col min="5" max="5" width="50.83203125" customWidth="1"/>
+    <col min="6" max="6" width="20.83203125" customWidth="1"/>
     <col min="7" max="7" width="35.83203125" customWidth="1"/>
     <col min="8" max="8" width="35.83203125" customWidth="1"/>
     <col min="9" max="9" width="35.83203125" customWidth="1"/>
@@ -423,29 +423,6 @@
     <col min="22" max="22" width="35.83203125" customWidth="1"/>
     <col min="23" max="23" width="35.83203125" customWidth="1"/>
     <col min="24" max="24" width="35.83203125" customWidth="1"/>
-    <col min="25" max="25" width="35.83203125" customWidth="1"/>
-    <col min="26" max="26" width="35.83203125" customWidth="1"/>
-    <col min="27" max="27" width="35.83203125" customWidth="1"/>
-    <col min="28" max="28" width="35.83203125" customWidth="1"/>
-    <col min="29" max="29" width="35.83203125" customWidth="1"/>
-    <col min="30" max="30" width="35.83203125" customWidth="1"/>
-    <col min="31" max="31" width="35.83203125" customWidth="1"/>
-    <col min="32" max="32" width="35.83203125" customWidth="1"/>
-    <col min="33" max="33" width="35.83203125" customWidth="1"/>
-    <col min="34" max="34" width="35.83203125" customWidth="1"/>
-    <col min="35" max="35" width="35.83203125" customWidth="1"/>
-    <col min="36" max="36" width="35.83203125" customWidth="1"/>
-    <col min="37" max="37" width="35.83203125" customWidth="1"/>
-    <col min="38" max="38" width="35.83203125" customWidth="1"/>
-    <col min="39" max="39" width="35.83203125" customWidth="1"/>
-    <col min="40" max="40" width="35.83203125" customWidth="1"/>
-    <col min="41" max="41" width="35.83203125" customWidth="1"/>
-    <col min="42" max="42" width="35.83203125" customWidth="1"/>
-    <col min="43" max="43" width="35.83203125" customWidth="1"/>
-    <col min="44" max="44" width="35.83203125" customWidth="1"/>
-    <col min="45" max="45" width="35.83203125" customWidth="1"/>
-    <col min="46" max="46" width="35.83203125" customWidth="1"/>
-    <col min="47" max="47" width="35.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -462,132 +439,63 @@
         <v>Imagen Local</v>
       </c>
       <c r="E1" t="str">
+        <v>Sinopsis</v>
+      </c>
+      <c r="F1" t="str">
         <v>En Varias Partes</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>Mega</v>
       </c>
-      <c r="G1" t="str">
-        <v>Mega Parte 1</v>
-      </c>
       <c r="H1" t="str">
-        <v>Mega Parte 2</v>
+        <v>Mediafire</v>
       </c>
       <c r="I1" t="str">
-        <v>Mega Parte 3</v>
+        <v>1Fichier</v>
       </c>
       <c r="J1" t="str">
-        <v>Mega Parte 4</v>
+        <v>Google Drive</v>
       </c>
       <c r="K1" t="str">
-        <v>Mediafire</v>
+        <v>Qiwi</v>
       </c>
       <c r="L1" t="str">
-        <v>Mediafire Parte 1</v>
+        <v>Pixeldrain</v>
       </c>
       <c r="M1" t="str">
-        <v>Mediafire Parte 2</v>
+        <v>Megaup</v>
       </c>
       <c r="N1" t="str">
-        <v>Mediafire Parte 3</v>
+        <v>Otro Link 1</v>
       </c>
       <c r="O1" t="str">
-        <v>Mediafire Parte 4</v>
+        <v>Otro Link 2</v>
       </c>
       <c r="P1" t="str">
-        <v>Mediafire Parte 5</v>
+        <v>Otro Link 3</v>
       </c>
       <c r="Q1" t="str">
-        <v>Mediafire Parte 6</v>
+        <v>Otro Link 4</v>
       </c>
       <c r="R1" t="str">
-        <v>Mediafire Parte 7</v>
+        <v>Otro Link 5</v>
       </c>
       <c r="S1" t="str">
-        <v>Mediafire Parte 8</v>
+        <v>Otro Link 6</v>
       </c>
       <c r="T1" t="str">
-        <v>Mediafire Parte 9</v>
+        <v>Otro Link 7</v>
       </c>
       <c r="U1" t="str">
-        <v>Mediafire Parte 10</v>
+        <v>Otro Link 8</v>
       </c>
       <c r="V1" t="str">
-        <v>Mediafire Parte 11</v>
+        <v>Otro Link 9</v>
       </c>
       <c r="W1" t="str">
-        <v>1Fichier</v>
+        <v>Otro Link 10</v>
       </c>
       <c r="X1" t="str">
-        <v>1Fichier Parte 1</v>
-      </c>
-      <c r="Y1" t="str">
-        <v>1Fichier Parte 2</v>
-      </c>
-      <c r="Z1" t="str">
-        <v>1Fichier Parte 3</v>
-      </c>
-      <c r="AA1" t="str">
-        <v>1Fichier Parte 4</v>
-      </c>
-      <c r="AB1" t="str">
-        <v>1Fichier Parte 5</v>
-      </c>
-      <c r="AC1" t="str">
-        <v>1Fichier Parte 6</v>
-      </c>
-      <c r="AD1" t="str">
-        <v>Google Drive</v>
-      </c>
-      <c r="AE1" t="str">
-        <v>Google Drive Parte 1</v>
-      </c>
-      <c r="AF1" t="str">
-        <v>Google Drive Parte 2</v>
-      </c>
-      <c r="AG1" t="str">
-        <v>Google Drive Parte 3</v>
-      </c>
-      <c r="AH1" t="str">
-        <v>Qiwi</v>
-      </c>
-      <c r="AI1" t="str">
-        <v>Pixeldrain</v>
-      </c>
-      <c r="AJ1" t="str">
-        <v>Megaup</v>
-      </c>
-      <c r="AK1" t="str">
-        <v>Otro Link 1</v>
-      </c>
-      <c r="AL1" t="str">
-        <v>Otro Link 2</v>
-      </c>
-      <c r="AM1" t="str">
-        <v>Otro Link 3</v>
-      </c>
-      <c r="AN1" t="str">
-        <v>Otro Link 4</v>
-      </c>
-      <c r="AO1" t="str">
-        <v>Otro Link 5</v>
-      </c>
-      <c r="AP1" t="str">
-        <v>Otro Link 6</v>
-      </c>
-      <c r="AQ1" t="str">
-        <v>Otro Link 7</v>
-      </c>
-      <c r="AR1" t="str">
-        <v>Otro Link 8</v>
-      </c>
-      <c r="AS1" t="str">
-        <v>Otro Link 9</v>
-      </c>
-      <c r="AT1" t="str">
-        <v>Otro Link 10</v>
-      </c>
-      <c r="AU1" t="str">
         <v>Otro Link 11</v>
       </c>
     </row>
@@ -605,27 +513,24 @@
         <v>imagenes/PS3/Just Dance Unlimited.jpg</v>
       </c>
       <c r="E2" t="str">
-        <v>No</v>
+        <v>No disponible</v>
       </c>
       <c r="F2" t="str">
+        <v>No</v>
+      </c>
+      <c r="G2" t="str">
         <v>https://mega.nz/folder/BBcnjYCK#oJZzG4SPK7i7kMF7k22soA</v>
       </c>
-      <c r="L2" t="str">
-        <v>https://www.mediafire.com/folder/29ocmx4di28ja/Just_Dance_Unlimited_PS3</v>
-      </c>
-      <c r="M2" t="str">
-        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
-      </c>
-      <c r="AD2" t="str">
+      <c r="J2" t="str">
         <v>https://drive.google.com/drive/folders/1nDFJPNm59b5boWvNL9Ytp9VK4qZ4igiM</v>
       </c>
-      <c r="AK2" t="str">
-        <v>https://gamepciso.com/</v>
-      </c>
-      <c r="AL2" t="str">
-        <v>https://downloadgameps3.net/archives/18667</v>
-      </c>
-      <c r="AM2" t="str">
+      <c r="N2" t="str">
+        <v>https://gamepciso.com/</v>
+      </c>
+      <c r="O2" t="str">
+        <v>https://downloadgameps3.net/archives/18667</v>
+      </c>
+      <c r="P2" t="str">
         <v>https://dlpsgame.com/guide-jdownloader-2/</v>
       </c>
     </row>
@@ -643,18 +548,21 @@
         <v>imagenes/PS3/Just Dance 2023 Mod.jpg</v>
       </c>
       <c r="E3" t="str">
-        <v>No</v>
-      </c>
-      <c r="K3" t="str">
-        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
-      </c>
-      <c r="AK3" t="str">
-        <v>https://gamepciso.com/</v>
-      </c>
-      <c r="AL3" t="str">
-        <v>https://downloadgameps3.net/archives/18667</v>
-      </c>
-      <c r="AM3" t="str">
+        <v>No disponible</v>
+      </c>
+      <c r="F3" t="str">
+        <v>No</v>
+      </c>
+      <c r="H3" t="str">
+        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
+      </c>
+      <c r="N3" t="str">
+        <v>https://gamepciso.com/</v>
+      </c>
+      <c r="O3" t="str">
+        <v>https://downloadgameps3.net/archives/18667</v>
+      </c>
+      <c r="P3" t="str">
         <v>https://dlpsgame.com/guide-jdownloader-2/</v>
       </c>
     </row>
@@ -672,27 +580,24 @@
         <v>imagenes/PS3/Just Dance 2022 Mod.jpg</v>
       </c>
       <c r="E4" t="str">
-        <v>No</v>
+        <v>No disponible</v>
       </c>
       <c r="F4" t="str">
+        <v>No</v>
+      </c>
+      <c r="G4" t="str">
         <v>https://filecrypt.cc/Container/C17027B63D.html</v>
       </c>
-      <c r="L4" t="str">
-        <v>https://filecrypt.cc/Container/986064EE73.html</v>
-      </c>
-      <c r="M4" t="str">
-        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
-      </c>
-      <c r="AK4" t="str">
+      <c r="N4" t="str">
         <v>https://filecrypt.cc/Container/C1D71FBAA5.html</v>
       </c>
-      <c r="AL4" t="str">
-        <v>https://gamepciso.com/</v>
-      </c>
-      <c r="AM4" t="str">
-        <v>https://downloadgameps3.net/archives/18667</v>
-      </c>
-      <c r="AN4" t="str">
+      <c r="O4" t="str">
+        <v>https://gamepciso.com/</v>
+      </c>
+      <c r="P4" t="str">
+        <v>https://downloadgameps3.net/archives/18667</v>
+      </c>
+      <c r="Q4" t="str">
         <v>https://dlpsgame.com/guide-jdownloader-2/</v>
       </c>
     </row>
@@ -710,48 +615,33 @@
         <v>imagenes/PS3/Life Is Strange PSN.jpg</v>
       </c>
       <c r="E5" t="str">
-        <v>No</v>
-      </c>
-      <c r="L5" t="str">
-        <v>https://www.mediafire.com/file/jtki3pz7k0pxeqb/L_31636-USA-Game-EP1-5-PS3-[DLPSGAME.COM].rar/file</v>
-      </c>
-      <c r="M5" t="str">
-        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
-      </c>
-      <c r="X5" t="str">
-        <v>https://1fichier.com/?2bsedbxdiq02yugsyyyr</v>
-      </c>
-      <c r="Y5" t="str">
-        <v>https://1fichier.com/?j0ownfh3c6ygpt8xk7tc</v>
-      </c>
-      <c r="Z5" t="str">
-        <v>https://1fichier.com/?1ff8r0h6omrhbpo3cibu</v>
-      </c>
-      <c r="AA5" t="str">
-        <v>https://1fichier.com/?aa3b8gr70t</v>
-      </c>
-      <c r="AK5" t="str">
+        <v>No disponible</v>
+      </c>
+      <c r="F5" t="str">
+        <v>No</v>
+      </c>
+      <c r="N5" t="str">
         <v>https://filecrypt.cc/Container/6F7A49902A.html</v>
       </c>
-      <c r="AL5" t="str">
+      <c r="O5" t="str">
         <v>https://filecrypt.cc/Container/7697D15A70.html</v>
       </c>
-      <c r="AM5" t="str">
+      <c r="P5" t="str">
         <v>https://downloadgameps3.net/archives/20468</v>
       </c>
-      <c r="AN5" t="str">
+      <c r="Q5" t="str">
         <v>https://downloadgameps3.net/archives/2703</v>
       </c>
-      <c r="AO5" t="str">
+      <c r="R5" t="str">
         <v>https://downloadgameps3.net/archives/2705</v>
       </c>
-      <c r="AP5" t="str">
-        <v>https://gamepciso.com/</v>
-      </c>
-      <c r="AQ5" t="str">
-        <v>https://downloadgameps3.net/archives/18667</v>
-      </c>
-      <c r="AR5" t="str">
+      <c r="S5" t="str">
+        <v>https://gamepciso.com/</v>
+      </c>
+      <c r="T5" t="str">
+        <v>https://downloadgameps3.net/archives/18667</v>
+      </c>
+      <c r="U5" t="str">
         <v>https://dlpsgame.com/guide-jdownloader-2/</v>
       </c>
     </row>
@@ -769,24 +659,21 @@
         <v>imagenes/PS3/Just Dance 2021 Mod.jpg</v>
       </c>
       <c r="E6" t="str">
-        <v>No</v>
-      </c>
-      <c r="L6" t="str">
-        <v>https://filecrypt.cc/Container/9FD544CF52.html</v>
-      </c>
-      <c r="M6" t="str">
-        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
-      </c>
-      <c r="AK6" t="str">
+        <v>No disponible</v>
+      </c>
+      <c r="F6" t="str">
+        <v>No</v>
+      </c>
+      <c r="N6" t="str">
         <v>https://filecrypt.cc/Container/36C5839610.html</v>
       </c>
-      <c r="AL6" t="str">
-        <v>https://gamepciso.com/</v>
-      </c>
-      <c r="AM6" t="str">
-        <v>https://downloadgameps3.net/archives/18667</v>
-      </c>
-      <c r="AN6" t="str">
+      <c r="O6" t="str">
+        <v>https://gamepciso.com/</v>
+      </c>
+      <c r="P6" t="str">
+        <v>https://downloadgameps3.net/archives/18667</v>
+      </c>
+      <c r="Q6" t="str">
         <v>https://dlpsgame.com/guide-jdownloader-2/</v>
       </c>
     </row>
@@ -804,24 +691,21 @@
         <v>imagenes/PS3/FIFA 21 Mod.jpg</v>
       </c>
       <c r="E7" t="str">
-        <v>No</v>
-      </c>
-      <c r="K7" t="str">
-        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
-      </c>
-      <c r="X7" t="str">
-        <v>https://1fichier.com/?zw50ogagot85d5inpaes</v>
-      </c>
-      <c r="Y7" t="str">
-        <v>https://1fichier.com/?any9x8ns2o49f8hu2jq1</v>
-      </c>
-      <c r="AK7" t="str">
-        <v>https://downloadgameps3.net/archives/18667</v>
-      </c>
-      <c r="AL7" t="str">
+        <v>No disponible</v>
+      </c>
+      <c r="F7" t="str">
+        <v>No</v>
+      </c>
+      <c r="H7" t="str">
+        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
+      </c>
+      <c r="N7" t="str">
+        <v>https://downloadgameps3.net/archives/18667</v>
+      </c>
+      <c r="O7" t="str">
         <v>https://dlpsgame.com/guide-download-game-use-jdownload/</v>
       </c>
-      <c r="AM7" t="str">
+      <c r="P7" t="str">
         <v>https://dlpsgame.com/guide-jdownloader-2/</v>
       </c>
     </row>
@@ -839,24 +723,21 @@
         <v>imagenes/PS3/Just Dance 2020 Mod.jpg</v>
       </c>
       <c r="E8" t="str">
-        <v>No</v>
+        <v>No disponible</v>
       </c>
       <c r="F8" t="str">
+        <v>No</v>
+      </c>
+      <c r="G8" t="str">
         <v>https://filecrypt.cc/Container/DD51965B0F.html</v>
       </c>
-      <c r="L8" t="str">
-        <v>https://filecrypt.cc/Container/318AADDE40.html</v>
-      </c>
-      <c r="M8" t="str">
-        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
-      </c>
-      <c r="AK8" t="str">
-        <v>https://gamepciso.com/</v>
-      </c>
-      <c r="AL8" t="str">
-        <v>https://downloadgameps3.net/archives/18667</v>
-      </c>
-      <c r="AM8" t="str">
+      <c r="N8" t="str">
+        <v>https://gamepciso.com/</v>
+      </c>
+      <c r="O8" t="str">
+        <v>https://downloadgameps3.net/archives/18667</v>
+      </c>
+      <c r="P8" t="str">
         <v>https://dlpsgame.com/guide-jdownloader-2/</v>
       </c>
     </row>
@@ -874,33 +755,24 @@
         <v>imagenes/PS3/Just Dance 2019 Mod.jpg</v>
       </c>
       <c r="E9" t="str">
-        <v>No</v>
-      </c>
-      <c r="L9" t="str">
-        <v>https://filecrypt.cc/Container/9FCB888DAF.html</v>
-      </c>
-      <c r="M9" t="str">
-        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
-      </c>
-      <c r="X9" t="str">
-        <v>https://filecrypt.cc/Container/6122618C5C.html</v>
-      </c>
-      <c r="Y9" t="str">
-        <v>https://downloadgameps3.net/archives/2677</v>
-      </c>
-      <c r="AK9" t="str">
+        <v>No disponible</v>
+      </c>
+      <c r="F9" t="str">
+        <v>No</v>
+      </c>
+      <c r="N9" t="str">
         <v>https://filecrypt.cc/Container/4AE6520C6E.html</v>
       </c>
-      <c r="AL9" t="str">
-        <v>https://downloadgameps3.net/archives/18667</v>
-      </c>
-      <c r="AM9" t="str">
+      <c r="O9" t="str">
+        <v>https://downloadgameps3.net/archives/18667</v>
+      </c>
+      <c r="P9" t="str">
         <v>https://dlpsgame.com/guide-download-game-use-jdownload/</v>
       </c>
-      <c r="AN9" t="str">
-        <v>https://gamepciso.com/</v>
-      </c>
-      <c r="AO9" t="str">
+      <c r="Q9" t="str">
+        <v>https://gamepciso.com/</v>
+      </c>
+      <c r="R9" t="str">
         <v>https://dlpsgame.com/guide-jdownloader-2/</v>
       </c>
     </row>
@@ -918,63 +790,30 @@
         <v>imagenes/PS3/FIFA 19.jpg</v>
       </c>
       <c r="E10" t="str">
-        <v>No</v>
-      </c>
-      <c r="G10" t="str">
-        <v>https://filecrypt.cc/Container/FC4AB648AA.html</v>
-      </c>
-      <c r="H10" t="str">
-        <v>https://filecrypt.cc/Container/85BA0A108D.html</v>
-      </c>
-      <c r="I10" t="str">
-        <v>https://filecrypt.cc/Container/6981CBE456.html</v>
-      </c>
-      <c r="L10" t="str">
-        <v>https://filecrypt.cc/Container/7F7A478DDE.html</v>
-      </c>
-      <c r="M10" t="str">
-        <v>https://filecrypt.cc/Container/77EADC4A86.html</v>
+        <v>No disponible</v>
+      </c>
+      <c r="F10" t="str">
+        <v>No</v>
       </c>
       <c r="N10" t="str">
-        <v>https://filecrypt.cc/Container/D38A4D83FB.html</v>
+        <v>https://downloadgameps3.net/archives/9384</v>
       </c>
       <c r="O10" t="str">
-        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
-      </c>
-      <c r="X10" t="str">
-        <v>https://1fichier.com/?nmatahllpmgwflhdnbbc</v>
-      </c>
-      <c r="Y10" t="str">
-        <v>https://1fichier.com/?gvni00k9y7d8to3c1hth</v>
-      </c>
-      <c r="Z10" t="str">
-        <v>https://1fichier.com/?7entw4prumdzwo7zrp4z</v>
-      </c>
-      <c r="AA10" t="str">
-        <v>https://filecrypt.cc/Container/616691CC72.html</v>
-      </c>
-      <c r="AB10" t="str">
-        <v>https://filecrypt.cc/Container/A6807438A6.html</v>
-      </c>
-      <c r="AK10" t="str">
-        <v>https://downloadgameps3.net/archives/9384</v>
-      </c>
-      <c r="AL10" t="str">
-        <v>https://downloadgameps3.net/archives/18667</v>
-      </c>
-      <c r="AM10" t="str">
+        <v>https://downloadgameps3.net/archives/18667</v>
+      </c>
+      <c r="P10" t="str">
         <v>https://dlpsgame.com/guide-download-game-use-jdownload/</v>
       </c>
-      <c r="AN10" t="str">
+      <c r="Q10" t="str">
         <v>https://downloadgameps3.net/archives/9386</v>
       </c>
-      <c r="AO10" t="str">
-        <v>https://gamepciso.com/</v>
-      </c>
-      <c r="AP10" t="str">
+      <c r="R10" t="str">
+        <v>https://gamepciso.com/</v>
+      </c>
+      <c r="S10" t="str">
         <v>https://filecrypt.cc/Container/26EA22B8CF.html</v>
       </c>
-      <c r="AQ10" t="str">
+      <c r="T10" t="str">
         <v>https://dlpsgame.com/guide-jdownloader-2/</v>
       </c>
     </row>
@@ -992,33 +831,27 @@
         <v>imagenes/PS3/Just Dance 2018.jpg</v>
       </c>
       <c r="E11" t="str">
-        <v>No</v>
-      </c>
-      <c r="K11" t="str">
-        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
-      </c>
-      <c r="X11" t="str">
-        <v>https://1fichier.com/?xvatj7tz3v3fbvjqp2rg</v>
-      </c>
-      <c r="Y11" t="str">
-        <v>https://1fichier.com/?8zkcrx6j8rkk2e244s54</v>
-      </c>
-      <c r="Z11" t="str">
-        <v>https://1fichier.com/?ummkputqc1v7eox9fv33</v>
-      </c>
-      <c r="AK11" t="str">
+        <v>No disponible</v>
+      </c>
+      <c r="F11" t="str">
+        <v>No</v>
+      </c>
+      <c r="H11" t="str">
+        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
+      </c>
+      <c r="N11" t="str">
         <v>https://downloadgameps3.net/archives/10096</v>
       </c>
-      <c r="AL11" t="str">
+      <c r="O11" t="str">
         <v>https://downloadgameps3.net/archives/10098</v>
       </c>
-      <c r="AM11" t="str">
-        <v>https://gamepciso.com/</v>
-      </c>
-      <c r="AN11" t="str">
-        <v>https://downloadgameps3.net/archives/18667</v>
-      </c>
-      <c r="AO11" t="str">
+      <c r="P11" t="str">
+        <v>https://gamepciso.com/</v>
+      </c>
+      <c r="Q11" t="str">
+        <v>https://downloadgameps3.net/archives/18667</v>
+      </c>
+      <c r="R11" t="str">
         <v>https://dlpsgame.com/guide-jdownloader-2/</v>
       </c>
     </row>
@@ -1036,45 +869,27 @@
         <v>imagenes/PS3/FIFA 18.jpg</v>
       </c>
       <c r="E12" t="str">
-        <v>No</v>
-      </c>
-      <c r="G12" t="str">
-        <v>https://filecrypt.cc/Container/A8B1D5E655.html</v>
-      </c>
-      <c r="H12" t="str">
-        <v>https://filecrypt.cc/Container/201710BE6E.html</v>
-      </c>
-      <c r="L12" t="str">
-        <v>https://filecrypt.cc/Container/855DEA0275.html</v>
-      </c>
-      <c r="M12" t="str">
-        <v>https://filecrypt.cc/Container/6C1DD8C520.html</v>
+        <v>No disponible</v>
+      </c>
+      <c r="F12" t="str">
+        <v>No</v>
       </c>
       <c r="N12" t="str">
-        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
-      </c>
-      <c r="X12" t="str">
-        <v>https://1fichier.com/?kuu3wian1yhom4ipkq0f</v>
-      </c>
-      <c r="Y12" t="str">
-        <v>https://1fichier.com/?lk3h5emdcbs352lgo98a</v>
-      </c>
-      <c r="AK12" t="str">
         <v>https://goo.gl/U1hRKA</v>
       </c>
-      <c r="AL12" t="str">
+      <c r="O12" t="str">
         <v>https://downloadgameps3.net/archives/9380</v>
       </c>
-      <c r="AM12" t="str">
+      <c r="P12" t="str">
         <v>https://downloadgameps3.net/archives/9382</v>
       </c>
-      <c r="AN12" t="str">
+      <c r="Q12" t="str">
         <v>https://gamepciso.com/fifa-18-download-free/</v>
       </c>
-      <c r="AO12" t="str">
-        <v>https://downloadgameps3.net/archives/18667</v>
-      </c>
-      <c r="AP12" t="str">
+      <c r="R12" t="str">
+        <v>https://downloadgameps3.net/archives/18667</v>
+      </c>
+      <c r="S12" t="str">
         <v>https://dlpsgame.com/guide-jdownloader-2/</v>
       </c>
     </row>
@@ -1092,69 +907,30 @@
         <v>imagenes/PS3/NBA 2K18.jpg</v>
       </c>
       <c r="E13" t="str">
-        <v>No</v>
-      </c>
-      <c r="G13" t="str">
-        <v>https://goo.gl/HwnZJg</v>
-      </c>
-      <c r="H13" t="str">
-        <v>https://filecrypt.cc/Container/9E99800482.html</v>
-      </c>
-      <c r="I13" t="str">
-        <v>https://goo.gl/aJR3hi</v>
-      </c>
-      <c r="J13" t="str">
-        <v>https://filecrypt.cc/Container/12FB9A0F6A.html</v>
-      </c>
-      <c r="L13" t="str">
-        <v>https://filecrypt.cc/Container/A5A55D398A.html</v>
-      </c>
-      <c r="M13" t="str">
-        <v>https://filecrypt.cc/Container/B64B8B86AD.html</v>
+        <v>No disponible</v>
+      </c>
+      <c r="F13" t="str">
+        <v>No</v>
       </c>
       <c r="N13" t="str">
-        <v>https://www.mediafire.com/folder/rp3u5hrs8kg24/NBA+2K18</v>
+        <v>https://downloadgameps3.net/archives/10954</v>
       </c>
       <c r="O13" t="str">
-        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
-      </c>
-      <c r="X13" t="str">
-        <v>https://1fichier.com/?uqmohdocwfgc9tv92icf</v>
-      </c>
-      <c r="Y13" t="str">
-        <v>https://1fichier.com/?jimr0cqvdgrf5od9elk8</v>
-      </c>
-      <c r="Z13" t="str">
-        <v>https://1fichier.com/?jdxyqctnhxd9aofb5gmk</v>
-      </c>
-      <c r="AA13" t="str">
-        <v>https://1fichier.com/?c4pfjvkryfz2f2belmzu</v>
-      </c>
-      <c r="AB13" t="str">
-        <v>https://x.com/intent/post?text=https://1fichier.com/?wifebb4pc7688xvtwuwzI%20uploaded%20a%20working%20game&amp;url=https%3A%2F%2Fdlpsgame.com%2Fnba-2k18-full-free%2F%23comment-125414</v>
-      </c>
-      <c r="AC13" t="str">
-        <v>https://1fichier.com/?wifebb4pc7688xvtwuwz: https://1fichier.com/?wifebb4pc7688xvtwuwz</v>
-      </c>
-      <c r="AK13" t="str">
-        <v>https://downloadgameps3.net/archives/10954</v>
-      </c>
-      <c r="AL13" t="str">
-        <v>https://downloadgameps3.net/archives/18667</v>
-      </c>
-      <c r="AM13" t="str">
+        <v>https://downloadgameps3.net/archives/18667</v>
+      </c>
+      <c r="P13" t="str">
         <v>https://dlpsgame.com/guide-download-game-use-jdownload/</v>
       </c>
-      <c r="AN13" t="str">
+      <c r="Q13" t="str">
         <v>https://downloadgameps3.net/archives/10956</v>
       </c>
-      <c r="AO13" t="str">
+      <c r="R13" t="str">
         <v>https://filecrypt.cc/Container/50B046AEE3.html</v>
       </c>
-      <c r="AP13" t="str">
+      <c r="S13" t="str">
         <v>https://gamepciso.com/nba-2k18-download-free/</v>
       </c>
-      <c r="AQ13" t="str">
+      <c r="T13" t="str">
         <v>https://dlpsgame.com/guide-jdownloader-2/</v>
       </c>
     </row>
@@ -1172,33 +948,24 @@
         <v>imagenes/PS3/Winning Eleven 2018.jpg</v>
       </c>
       <c r="E14" t="str">
-        <v>No</v>
-      </c>
-      <c r="G14" t="str">
-        <v>https://goo.gl/TqBbGm</v>
-      </c>
-      <c r="H14" t="str">
-        <v>https://filecrypt.cc/Container/618D1EF6E1.html</v>
-      </c>
-      <c r="L14" t="str">
-        <v>https://filecrypt.cc/Container/D8F4F290EA.html</v>
-      </c>
-      <c r="M14" t="str">
-        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
-      </c>
-      <c r="W14" t="str">
+        <v>No disponible</v>
+      </c>
+      <c r="F14" t="str">
+        <v>No</v>
+      </c>
+      <c r="I14" t="str">
         <v>https://1fichier.com/?qx7r1iw9un25vi7nsodm</v>
       </c>
-      <c r="AK14" t="str">
+      <c r="N14" t="str">
         <v>https://goo.gl/rcWqBe</v>
       </c>
-      <c r="AL14" t="str">
+      <c r="O14" t="str">
         <v>https://gamepciso.com/pro-evolution-soccer-2018-download-free/</v>
       </c>
-      <c r="AM14" t="str">
-        <v>https://downloadgameps3.net/archives/18667</v>
-      </c>
-      <c r="AN14" t="str">
+      <c r="P14" t="str">
+        <v>https://downloadgameps3.net/archives/18667</v>
+      </c>
+      <c r="Q14" t="str">
         <v>https://dlpsgame.com/guide-jdownloader-2/</v>
       </c>
     </row>
@@ -1216,102 +983,39 @@
         <v>imagenes/PS3/Pro Evolution Soccer 2018 [PES 2018].jpg</v>
       </c>
       <c r="E15" t="str">
+        <v>No disponible</v>
+      </c>
+      <c r="F15" t="str">
         <v>Sí</v>
       </c>
-      <c r="G15" t="str">
-        <v>https://filecrypt.cc/Container/C3AEED4F81.html</v>
-      </c>
-      <c r="H15" t="str">
-        <v>https://filecrypt.cc/Container/47860950C4.html</v>
-      </c>
-      <c r="I15" t="str">
-        <v>https://mega.nz/folder/oWxwXTDA#o8lOyYK7nA5MO3WjzaKHmQ: https://mega.nz/folder/oWxwXTDA#o8lOyYK7nA5MO3WjzaKHmQ</v>
-      </c>
-      <c r="L15" t="str">
-        <v>https://filecrypt.cc/Container/32EAED31AB.html</v>
-      </c>
-      <c r="M15" t="str">
-        <v>https://filecrypt.cc/Container/A6D9F64B40.html</v>
-      </c>
       <c r="N15" t="str">
-        <v>https://x.com/intent/post?text=PES%202018%20transfer%20winterhttps://www.mediafire.com/fil...%20&amp;url=https%3A%2F%2Fdlpsgame.com%2Fpro-evolution-soccer-2018-pes-2018-full-free%2F%23comment-183464</v>
+        <v>https://downloadgameps3.net/archives/11252</v>
       </c>
       <c r="O15" t="str">
-        <v>https://www.mediafire.com/file/wmo0b583pn6hlq2/PES20182023GEMBOX.txt/file: https://www.mediafire.com/file/wmo0b583pn6hlq2/PES20182023GEMBOX.txt/file</v>
+        <v>https://downloadgameps3.net/archives/214</v>
       </c>
       <c r="P15" t="str">
-        <v>https://www.mediafire.com/file/3nq1tae8fmkv20d/BLUS_Potato_Patch_V9_Parte_1_By_Team_Poltergeist.pkg/file?fbclid=IwAR0im_ZBN8rBOfjIVmfxf3-IhxgAuVX4GA83RSjP5m2UixhPO09KJzxoTz0: https://www.mediafire.com/file/3nq1tae8fmkv20d/BLUS_Potato_Patch_V9_Parte_1_By_Team_Poltergeist.pkg/file?fbclid=IwAR0im_ZBN8rBOfjIVmfxf3-IhxgAuVX4GA83RSjP5m2UixhPO09KJzxoTz0</v>
+        <v>https://downloadgameps3.net/archives/191</v>
       </c>
       <c r="Q15" t="str">
-        <v>https://www.mediafire.com/file/iq4ghokcxko7syt/BLUS_Potato_Patch_V9_Parte_2_By_Team_Poltergeist.pkg/file?fbclid=IwAR3iuPk5F26iI7dC5O2IKQpHWJ-JKx8YZEsLgYxhXmpiPgDMsZm2pPAgNms: https://www.mediafire.com/file/iq4ghokcxko7syt/BLUS_Potato_Patch_V9_Parte_2_By_Team_Poltergeist.pkg/file?fbclid=IwAR3iuPk5F26iI7dC5O2IKQpHWJ-JKx8YZEsLgYxhXmpiPgDMsZm2pPAgNms</v>
+        <v>https://downloadgameps3.net/archives/11250</v>
       </c>
       <c r="R15" t="str">
-        <v>https://www.mediafire.com/file/txh9rfvpq3qqbql/BLUS_Potato_Patch_V9_Parte_3_By_Team_Poltergeist.pkg/file?fbclid=IwAR1oRBmVoDj9hYMWim1ebc68c28l7LKK6lMhajWlNLu5XbOXS7B_ZBXbwMo: https://www.mediafire.com/file/txh9rfvpq3qqbql/BLUS_Potato_Patch_V9_Parte_3_By_Team_Poltergeist.pkg/file?fbclid=IwAR1oRBmVoDj9hYMWim1ebc68c28l7LKK6lMhajWlNLu5XbOXS7B_ZBXbwMo</v>
+        <v>https://downloadgameps3.net/archives/224</v>
       </c>
       <c r="S15" t="str">
-        <v>https://www.mediafire.com/file/ie69gwtyf6n98h9/BLUS_Potato_Patch_V9_Parte_4_By_Team_Poltergeist.pkg/file?fbclid=IwAR1Sqf7Yps_J53LbOgkcB11y_G_CpCW8_WbZs25qrsOnNt3nOOWQ0w3eInw: https://www.mediafire.com/file/ie69gwtyf6n98h9/BLUS_Potato_Patch_V9_Parte_4_By_Team_Poltergeist.pkg/file?fbclid=IwAR1Sqf7Yps_J53LbOgkcB11y_G_CpCW8_WbZs25qrsOnNt3nOOWQ0w3eInw</v>
+        <v>https://downloadgameps3.net/archives/226</v>
       </c>
       <c r="T15" t="str">
-        <v>https://www.mediafire.com/file/imxeek06lsp61e3/BLUS_Potato_Patch_V9_Parte_5_By_Team_Poltergeist.pkg/file?fbclid=IwAR17oVhUuW7akat05iOYx8mb_SmJnuOdy363wDHPxGpFQKFUjp2ritO6ekI: https://www.mediafire.com/file/imxeek06lsp61e3/BLUS_Potato_Patch_V9_Parte_5_By_Team_Poltergeist.pkg/file?fbclid=IwAR17oVhUuW7akat05iOYx8mb_SmJnuOdy363wDHPxGpFQKFUjp2ritO6ekI</v>
+        <v>https://downloadgameps3.net/archives/3462</v>
       </c>
       <c r="U15" t="str">
-        <v>https://www.mediafire.com/: https://www.mediafire.com/</v>
+        <v>https://gamepciso.com/pro-evolution-soccer-2018-download-free/</v>
       </c>
       <c r="V15" t="str">
-        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
-      </c>
-      <c r="X15" t="str">
-        <v>https://1fichier.com/?j5b2wj7l1ztg389ouaxk</v>
-      </c>
-      <c r="Y15" t="str">
-        <v>https://filecrypt.cc/Container/A014E77AE2.html</v>
-      </c>
-      <c r="Z15" t="str">
-        <v>https://1fichier.com/?anse4jof0j4iffvmjta5</v>
-      </c>
-      <c r="AA15" t="str">
-        <v>https://filecrypt.cc/Container/91AAE631C9.html</v>
-      </c>
-      <c r="AB15" t="str">
-        <v>https://filecrypt.cc/Container/74D1EBB80A.html</v>
-      </c>
-      <c r="AE15" t="str">
-        <v>https://x.com/intent/post?text=parte%201https://drive.google.com/file/d/1mtzUIU8xgCvma...%20&amp;url=https%3A%2F%2Fdlpsgame.com%2Fpro-evolution-soccer-2018-pes-2018-full-free%2F%23comment-115186</v>
-      </c>
-      <c r="AF15" t="str">
-        <v>https://drive.google.com/file/d/1mtzUIU8xgCvmad9ViRAL9UQNlXgfCARX/view?usp=sharing: https://drive.google.com/file/d/1mtzUIU8xgCvmad9ViRAL9UQNlXgfCARX/view?usp=sharing</v>
-      </c>
-      <c r="AG15" t="str">
-        <v>https://drive.google.com/file/d/1HlonkV7xBSQepTJDZjYu1Bnf7WjJZ6-g/view?usp=sharing: https://drive.google.com/file/d/1HlonkV7xBSQepTJDZjYu1Bnf7WjJZ6-g/view?usp=sharing</v>
-      </c>
-      <c r="AK15" t="str">
-        <v>https://downloadgameps3.net/archives/11252</v>
-      </c>
-      <c r="AL15" t="str">
-        <v>https://downloadgameps3.net/archives/214</v>
-      </c>
-      <c r="AM15" t="str">
-        <v>https://downloadgameps3.net/archives/191</v>
-      </c>
-      <c r="AN15" t="str">
-        <v>https://downloadgameps3.net/archives/11250</v>
-      </c>
-      <c r="AO15" t="str">
-        <v>https://downloadgameps3.net/archives/224</v>
-      </c>
-      <c r="AP15" t="str">
-        <v>https://downloadgameps3.net/archives/226</v>
-      </c>
-      <c r="AQ15" t="str">
-        <v>https://downloadgameps3.net/archives/3462</v>
-      </c>
-      <c r="AR15" t="str">
-        <v>https://gamepciso.com/pro-evolution-soccer-2018-download-free/</v>
-      </c>
-      <c r="AS15" t="str">
-        <v>https://downloadgameps3.net/archives/18667</v>
-      </c>
-      <c r="AT15" t="str">
+        <v>https://downloadgameps3.net/archives/18667</v>
+      </c>
+      <c r="W15" t="str">
         <v>https://dlpsgame.com/guide-jdownloader-2/</v>
       </c>
     </row>
@@ -1329,45 +1033,36 @@
         <v>imagenes/PS3/Disney Pixar Cars 3 Driven to Win.jpg</v>
       </c>
       <c r="E16" t="str">
-        <v>No</v>
-      </c>
-      <c r="G16" t="str">
-        <v>https://filecrypt.cc/Container/8C3A502E68.html</v>
-      </c>
-      <c r="H16" t="str">
-        <v>https://goo.gl/ZWdo1D</v>
-      </c>
-      <c r="L16" t="str">
-        <v>https://filecrypt.cc/Container/96D228A7A2.html</v>
-      </c>
-      <c r="M16" t="str">
-        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
-      </c>
-      <c r="W16" t="str">
+        <v>No disponible</v>
+      </c>
+      <c r="F16" t="str">
+        <v>No</v>
+      </c>
+      <c r="I16" t="str">
         <v>https://1fichier.com/?teqwmw079iysfdclv2gf</v>
       </c>
-      <c r="AD16" t="str">
+      <c r="J16" t="str">
         <v>https://dlpsgame.com/cars-3-driven-to-win-iso-free/#comment-116328: https://dlpsgame.com/cars-3-driven-to-win-iso-free/#comment-116328</v>
       </c>
-      <c r="AK16" t="str">
+      <c r="N16" t="str">
         <v>https://downloadgameps3.net/archives/8892</v>
       </c>
-      <c r="AL16" t="str">
+      <c r="O16" t="str">
         <v>https://anotepad.com/notes/qxcygid5</v>
       </c>
-      <c r="AM16" t="str">
+      <c r="P16" t="str">
         <v>https://downloadgameps3.net/archives/8894</v>
       </c>
-      <c r="AN16" t="str">
+      <c r="Q16" t="str">
         <v>https://filecrypt.cc/Container/B003EBC8E6.html</v>
       </c>
-      <c r="AO16" t="str">
-        <v>https://gamepciso.com/</v>
-      </c>
-      <c r="AP16" t="str">
-        <v>https://downloadgameps3.net/archives/18667</v>
-      </c>
-      <c r="AQ16" t="str">
+      <c r="R16" t="str">
+        <v>https://gamepciso.com/</v>
+      </c>
+      <c r="S16" t="str">
+        <v>https://downloadgameps3.net/archives/18667</v>
+      </c>
+      <c r="T16" t="str">
         <v>https://dlpsgame.com/guide-jdownloader-2/</v>
       </c>
     </row>
@@ -1385,21 +1080,18 @@
         <v>imagenes/PS3/Risk Urban Assault PSN.jpg</v>
       </c>
       <c r="E17" t="str">
-        <v>No</v>
-      </c>
-      <c r="L17" t="str">
-        <v>https://filecrypt.cc/Container/C6EC87C1C5.html</v>
-      </c>
-      <c r="M17" t="str">
-        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
-      </c>
-      <c r="AK17" t="str">
-        <v>https://gamepciso.com/</v>
-      </c>
-      <c r="AL17" t="str">
-        <v>https://downloadgameps3.net/archives/18667</v>
-      </c>
-      <c r="AM17" t="str">
+        <v>No disponible</v>
+      </c>
+      <c r="F17" t="str">
+        <v>No</v>
+      </c>
+      <c r="N17" t="str">
+        <v>https://gamepciso.com/</v>
+      </c>
+      <c r="O17" t="str">
+        <v>https://downloadgameps3.net/archives/18667</v>
+      </c>
+      <c r="P17" t="str">
         <v>https://dlpsgame.com/guide-jdownloader-2/</v>
       </c>
     </row>
@@ -1417,63 +1109,45 @@
         <v>imagenes/PS3/Persona 5.jpg</v>
       </c>
       <c r="E18" t="str">
-        <v>No</v>
-      </c>
-      <c r="G18" t="str">
-        <v>https://mega.nz/#!MeBRzQBZ!_yGHoiTf9-nuZTvbhr_bPFC6pRuz1RCzBzroR5QsDJk</v>
+        <v>No disponible</v>
+      </c>
+      <c r="F18" t="str">
+        <v>No</v>
       </c>
       <c r="H18" t="str">
-        <v>https://mega.nz/#!3FszkCCQ!IdXXIMCt6WO0qldur5syB3hVOTreH_z9F1lf_i6FPFQ</v>
-      </c>
-      <c r="K18" t="str">
-        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
-      </c>
-      <c r="X18" t="str">
-        <v>https://1fichier.com/?7o30gx7dh0r33yzzet6q</v>
-      </c>
-      <c r="Y18" t="str">
-        <v>https://1fichier.com/?kvf25qw6zmujm97ta6n5</v>
-      </c>
-      <c r="Z18" t="str">
-        <v>https://1fichier.com/?4w9gmgv8osy11twelflq</v>
-      </c>
-      <c r="AA18" t="str">
-        <v>https://1fichier.com/?343zu81ja4ab867xtptu</v>
-      </c>
-      <c r="AB18" t="str">
-        <v>https://1fichier.com/?b9sbeukp9c8jj95afl6t</v>
-      </c>
-      <c r="AD18" t="str">
+        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
+      </c>
+      <c r="J18" t="str">
         <v>https://dlpsgame.com/guide-fix-error-limit-download-google-drive/: https://dlpsgame.com/guide-fix-error-limit-download-google-drive/</v>
       </c>
-      <c r="AK18" t="str">
+      <c r="N18" t="str">
         <v>https://downloadgameps3.net/archives/11290</v>
       </c>
-      <c r="AL18" t="str">
+      <c r="O18" t="str">
         <v>https://downloadgameps3.net/archives/11292</v>
       </c>
-      <c r="AM18" t="str">
+      <c r="P18" t="str">
         <v>https://downloadgameps3.net/archives/4680</v>
       </c>
-      <c r="AN18" t="str">
+      <c r="Q18" t="str">
         <v>https://downloadgameps3.net/archives/4683</v>
       </c>
-      <c r="AO18" t="str">
+      <c r="R18" t="str">
         <v>https://downloadgameps3.net/archives/4685</v>
       </c>
-      <c r="AP18" t="str">
+      <c r="S18" t="str">
         <v>https://downloadgameps3.net/archives/11298</v>
       </c>
-      <c r="AQ18" t="str">
+      <c r="T18" t="str">
         <v>http://bit.ly/2G7O7Sz</v>
       </c>
-      <c r="AR18" t="str">
-        <v>https://gamepciso.com/</v>
-      </c>
-      <c r="AS18" t="str">
-        <v>https://downloadgameps3.net/archives/18667</v>
-      </c>
-      <c r="AT18" t="str">
+      <c r="U18" t="str">
+        <v>https://gamepciso.com/</v>
+      </c>
+      <c r="V18" t="str">
+        <v>https://downloadgameps3.net/archives/18667</v>
+      </c>
+      <c r="W18" t="str">
         <v>https://dlpsgame.com/guide-jdownloader-2/</v>
       </c>
     </row>
@@ -1491,24 +1165,27 @@
         <v>imagenes/PS3/Sengoku Musou Sanada Maru.jpg</v>
       </c>
       <c r="E19" t="str">
-        <v>No</v>
-      </c>
-      <c r="K19" t="str">
-        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
-      </c>
-      <c r="W19" t="str">
+        <v>No disponible</v>
+      </c>
+      <c r="F19" t="str">
+        <v>No</v>
+      </c>
+      <c r="H19" t="str">
+        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
+      </c>
+      <c r="I19" t="str">
         <v>https://1fichier.com/?jdj8phls72beb1pw79ip</v>
       </c>
-      <c r="AK19" t="str">
+      <c r="N19" t="str">
         <v>https://downloadgameps3.net/archives/11768</v>
       </c>
-      <c r="AL19" t="str">
-        <v>https://gamepciso.com/</v>
-      </c>
-      <c r="AM19" t="str">
-        <v>https://downloadgameps3.net/archives/18667</v>
-      </c>
-      <c r="AN19" t="str">
+      <c r="O19" t="str">
+        <v>https://gamepciso.com/</v>
+      </c>
+      <c r="P19" t="str">
+        <v>https://downloadgameps3.net/archives/18667</v>
+      </c>
+      <c r="Q19" t="str">
         <v>https://dlpsgame.com/guide-jdownloader-2/</v>
       </c>
     </row>
@@ -1526,27 +1203,24 @@
         <v>imagenes/PS3/99 Vidas The Game PSN.jpg</v>
       </c>
       <c r="E20" t="str">
-        <v>No</v>
-      </c>
-      <c r="G20" t="str">
-        <v>https://x.com/intent/post?text=fix%20game%20link:%20https://mega.nz/#!hXACzAiT!J_QkgN4RN2U-fT2_bgdglQak82VHfs...%20&amp;url=https%3A%2F%2Fdlpsgame.com%2F99-vidas-game-psn-full-free%2F%23comment-42987</v>
+        <v>No disponible</v>
+      </c>
+      <c r="F20" t="str">
+        <v>No</v>
       </c>
       <c r="H20" t="str">
-        <v>https://mega.nz/#!hXACzAiT!J_QkgN4RN2U-fT2_bgdglQak82VHfsQLvW7rJfoZzUY: https://mega.nz/#!hXACzAiT!J_QkgN4RN2U-fT2_bgdglQak82VHfsQLvW7rJfoZzUY</v>
-      </c>
-      <c r="K20" t="str">
-        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
-      </c>
-      <c r="AK20" t="str">
+        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
+      </c>
+      <c r="N20" t="str">
         <v>https://downloadgameps3.net/archives/3377</v>
       </c>
-      <c r="AL20" t="str">
-        <v>https://gamepciso.com/</v>
-      </c>
-      <c r="AM20" t="str">
-        <v>https://downloadgameps3.net/archives/18667</v>
-      </c>
-      <c r="AN20" t="str">
+      <c r="O20" t="str">
+        <v>https://gamepciso.com/</v>
+      </c>
+      <c r="P20" t="str">
+        <v>https://downloadgameps3.net/archives/18667</v>
+      </c>
+      <c r="Q20" t="str">
         <v>https://dlpsgame.com/guide-jdownloader-2/</v>
       </c>
     </row>
@@ -1564,21 +1238,24 @@
         <v>imagenes/PS3/Steredenn PSN.jpg</v>
       </c>
       <c r="E21" t="str">
-        <v>No</v>
-      </c>
-      <c r="K21" t="str">
-        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
-      </c>
-      <c r="AK21" t="str">
+        <v>No disponible</v>
+      </c>
+      <c r="F21" t="str">
+        <v>No</v>
+      </c>
+      <c r="H21" t="str">
+        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
+      </c>
+      <c r="N21" t="str">
         <v>https://downloadgameps3.net/archives/5831</v>
       </c>
-      <c r="AL21" t="str">
-        <v>https://gamepciso.com/</v>
-      </c>
-      <c r="AM21" t="str">
-        <v>https://downloadgameps3.net/archives/18667</v>
-      </c>
-      <c r="AN21" t="str">
+      <c r="O21" t="str">
+        <v>https://gamepciso.com/</v>
+      </c>
+      <c r="P21" t="str">
+        <v>https://downloadgameps3.net/archives/18667</v>
+      </c>
+      <c r="Q21" t="str">
         <v>https://dlpsgame.com/guide-jdownloader-2/</v>
       </c>
     </row>
@@ -1596,21 +1273,24 @@
         <v>imagenes/PS3/Revenant Saga PSN.jpg</v>
       </c>
       <c r="E22" t="str">
-        <v>No</v>
+        <v>No disponible</v>
       </c>
       <c r="F22" t="str">
+        <v>No</v>
+      </c>
+      <c r="G22" t="str">
         <v>https://filecrypt.cc/Container/F494E4145F.html</v>
       </c>
-      <c r="K22" t="str">
-        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
-      </c>
-      <c r="AK22" t="str">
-        <v>https://gamepciso.com/</v>
-      </c>
-      <c r="AL22" t="str">
-        <v>https://downloadgameps3.net/archives/18667</v>
-      </c>
-      <c r="AM22" t="str">
+      <c r="H22" t="str">
+        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
+      </c>
+      <c r="N22" t="str">
+        <v>https://gamepciso.com/</v>
+      </c>
+      <c r="O22" t="str">
+        <v>https://downloadgameps3.net/archives/18667</v>
+      </c>
+      <c r="P22" t="str">
         <v>https://dlpsgame.com/guide-jdownloader-2/</v>
       </c>
     </row>
@@ -1628,30 +1308,27 @@
         <v>imagenes/PS3/Guilty Gear Xrd Rev 2 PSN.jpg</v>
       </c>
       <c r="E23" t="str">
-        <v>No</v>
+        <v>No disponible</v>
       </c>
       <c r="F23" t="str">
+        <v>No</v>
+      </c>
+      <c r="G23" t="str">
         <v>https://filecrypt.cc/Container/6C1DDF373E.html</v>
       </c>
-      <c r="L23" t="str">
-        <v>https://filecrypt.cc/Container/2C6AC908BC.html</v>
-      </c>
-      <c r="M23" t="str">
-        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
-      </c>
-      <c r="AK23" t="str">
+      <c r="N23" t="str">
         <v>https://downloadgameps3.net/archives/345</v>
       </c>
-      <c r="AL23" t="str">
+      <c r="O23" t="str">
         <v>https://downloadgameps3.net/archives/17096</v>
       </c>
-      <c r="AM23" t="str">
-        <v>https://gamepciso.com/</v>
-      </c>
-      <c r="AN23" t="str">
-        <v>https://downloadgameps3.net/archives/18667</v>
-      </c>
-      <c r="AO23" t="str">
+      <c r="P23" t="str">
+        <v>https://gamepciso.com/</v>
+      </c>
+      <c r="Q23" t="str">
+        <v>https://downloadgameps3.net/archives/18667</v>
+      </c>
+      <c r="R23" t="str">
         <v>https://dlpsgame.com/guide-jdownloader-2/</v>
       </c>
     </row>
@@ -1669,18 +1346,21 @@
         <v>imagenes/PS3/Rainbow Skies PSN.jpg</v>
       </c>
       <c r="E24" t="str">
-        <v>No</v>
-      </c>
-      <c r="K24" t="str">
-        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
-      </c>
-      <c r="AK24" t="str">
-        <v>https://gamepciso.com/</v>
-      </c>
-      <c r="AL24" t="str">
-        <v>https://downloadgameps3.net/archives/18667</v>
-      </c>
-      <c r="AM24" t="str">
+        <v>No disponible</v>
+      </c>
+      <c r="F24" t="str">
+        <v>No</v>
+      </c>
+      <c r="H24" t="str">
+        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
+      </c>
+      <c r="N24" t="str">
+        <v>https://gamepciso.com/</v>
+      </c>
+      <c r="O24" t="str">
+        <v>https://downloadgameps3.net/archives/18667</v>
+      </c>
+      <c r="P24" t="str">
         <v>https://dlpsgame.com/guide-jdownloader-2/</v>
       </c>
     </row>
@@ -1698,27 +1378,24 @@
         <v>imagenes/PS3/Berserk Musou PSN.jpg</v>
       </c>
       <c r="E25" t="str">
-        <v>No</v>
-      </c>
-      <c r="K25" t="str">
-        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
-      </c>
-      <c r="W25" t="str">
+        <v>No disponible</v>
+      </c>
+      <c r="F25" t="str">
+        <v>No</v>
+      </c>
+      <c r="H25" t="str">
+        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
+      </c>
+      <c r="I25" t="str">
         <v>https://1fichier.com/?9cqc0ewz1jblt392r5i6</v>
       </c>
-      <c r="AE25" t="str">
-        <v>https://drive.google.com/open?id=1lazODFHKBO5href-RS2-crvT0JghnLIU: https://drive.google.com/open?id=1lazODFHKBO5href-RS2-crvT0JghnLIU</v>
-      </c>
-      <c r="AF25" t="str">
-        <v>https://drive.google.com/open?id=1cUemJfpp6imk_u-FrVLD7DeX_7PYFT9S: https://drive.google.com/open?id=1cUemJfpp6imk_u-FrVLD7DeX_7PYFT9S</v>
-      </c>
-      <c r="AK25" t="str">
-        <v>https://gamepciso.com/</v>
-      </c>
-      <c r="AL25" t="str">
-        <v>https://downloadgameps3.net/archives/18667</v>
-      </c>
-      <c r="AM25" t="str">
+      <c r="N25" t="str">
+        <v>https://gamepciso.com/</v>
+      </c>
+      <c r="O25" t="str">
+        <v>https://downloadgameps3.net/archives/18667</v>
+      </c>
+      <c r="P25" t="str">
         <v>https://dlpsgame.com/guide-jdownloader-2/</v>
       </c>
     </row>
@@ -1736,45 +1413,36 @@
         <v>imagenes/PS3/Dragon Quest Builders Alefgard o Fukkatsu Niseyo.jpg</v>
       </c>
       <c r="E26" t="str">
-        <v>No</v>
+        <v>No disponible</v>
       </c>
       <c r="F26" t="str">
+        <v>No</v>
+      </c>
+      <c r="G26" t="str">
         <v>https://mega.nz/folder/Aj4FgRZJ#Zejes43IDnGqEkO8F1XZcg</v>
       </c>
-      <c r="K26" t="str">
-        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
-      </c>
-      <c r="X26" t="str">
-        <v>https://downloadgameps3.net/archives/6563</v>
-      </c>
-      <c r="Y26" t="str">
-        <v>https://downloadgameps3.net/archives/6565</v>
-      </c>
-      <c r="Z26" t="str">
-        <v>https://1fichier.com/?8i7fa4l2q9wgt8xkopvy</v>
-      </c>
-      <c r="AA26" t="str">
-        <v>https://1fichier.com/?fd3bjnd49xbphmtxx2vm</v>
-      </c>
-      <c r="AK26" t="str">
+      <c r="H26" t="str">
+        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
+      </c>
+      <c r="N26" t="str">
         <v>https://filecrypt.cc/Container/2A57DE85FE.html</v>
       </c>
-      <c r="AL26" t="str">
+      <c r="O26" t="str">
         <v>https://filecrypt.cc/Container/50DF3B7A02.html</v>
       </c>
-      <c r="AM26" t="str">
+      <c r="P26" t="str">
         <v>https://downloadgameps3.net/archives/8995</v>
       </c>
-      <c r="AN26" t="str">
-        <v>https://downloadgameps3.net/archives/18667</v>
-      </c>
-      <c r="AO26" t="str">
+      <c r="Q26" t="str">
+        <v>https://downloadgameps3.net/archives/18667</v>
+      </c>
+      <c r="R26" t="str">
         <v>https://dlpsgame.com/guide-download-game-use-jdownload/</v>
       </c>
-      <c r="AP26" t="str">
-        <v>https://gamepciso.com/</v>
-      </c>
-      <c r="AQ26" t="str">
+      <c r="S26" t="str">
+        <v>https://gamepciso.com/</v>
+      </c>
+      <c r="T26" t="str">
         <v>https://dlpsgame.com/guide-jdownloader-2/</v>
       </c>
     </row>
@@ -1792,21 +1460,24 @@
         <v>imagenes/PS3/Gradius 2 Gofer No Yabou PSN.jpg</v>
       </c>
       <c r="E27" t="str">
-        <v>No</v>
+        <v>No disponible</v>
       </c>
       <c r="F27" t="str">
+        <v>No</v>
+      </c>
+      <c r="G27" t="str">
         <v>https://goo.gl/Mssycd</v>
       </c>
-      <c r="K27" t="str">
-        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
-      </c>
-      <c r="AK27" t="str">
-        <v>https://gamepciso.com/</v>
-      </c>
-      <c r="AL27" t="str">
-        <v>https://downloadgameps3.net/archives/18667</v>
-      </c>
-      <c r="AM27" t="str">
+      <c r="H27" t="str">
+        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
+      </c>
+      <c r="N27" t="str">
+        <v>https://gamepciso.com/</v>
+      </c>
+      <c r="O27" t="str">
+        <v>https://downloadgameps3.net/archives/18667</v>
+      </c>
+      <c r="P27" t="str">
         <v>https://dlpsgame.com/guide-jdownloader-2/</v>
       </c>
     </row>
@@ -1824,21 +1495,24 @@
         <v>imagenes/PS3/Doodle Devil PSN.jpg</v>
       </c>
       <c r="E28" t="str">
-        <v>No</v>
+        <v>No disponible</v>
       </c>
       <c r="F28" t="str">
+        <v>No</v>
+      </c>
+      <c r="G28" t="str">
         <v>https://goo.gl/kXiWr2</v>
       </c>
-      <c r="K28" t="str">
-        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
-      </c>
-      <c r="AK28" t="str">
-        <v>https://gamepciso.com/</v>
-      </c>
-      <c r="AL28" t="str">
-        <v>https://downloadgameps3.net/archives/18667</v>
-      </c>
-      <c r="AM28" t="str">
+      <c r="H28" t="str">
+        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
+      </c>
+      <c r="N28" t="str">
+        <v>https://gamepciso.com/</v>
+      </c>
+      <c r="O28" t="str">
+        <v>https://downloadgameps3.net/archives/18667</v>
+      </c>
+      <c r="P28" t="str">
         <v>https://dlpsgame.com/guide-jdownloader-2/</v>
       </c>
     </row>
@@ -1856,18 +1530,21 @@
         <v>imagenes/PS3/Doodle Kingdom PSN.jpg</v>
       </c>
       <c r="E29" t="str">
-        <v>No</v>
-      </c>
-      <c r="K29" t="str">
-        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
-      </c>
-      <c r="AK29" t="str">
-        <v>https://gamepciso.com/</v>
-      </c>
-      <c r="AL29" t="str">
-        <v>https://downloadgameps3.net/archives/18667</v>
-      </c>
-      <c r="AM29" t="str">
+        <v>No disponible</v>
+      </c>
+      <c r="F29" t="str">
+        <v>No</v>
+      </c>
+      <c r="H29" t="str">
+        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
+      </c>
+      <c r="N29" t="str">
+        <v>https://gamepciso.com/</v>
+      </c>
+      <c r="O29" t="str">
+        <v>https://downloadgameps3.net/archives/18667</v>
+      </c>
+      <c r="P29" t="str">
         <v>https://dlpsgame.com/guide-jdownloader-2/</v>
       </c>
     </row>
@@ -1885,24 +1562,27 @@
         <v>imagenes/PS3/Handball 17.jpg</v>
       </c>
       <c r="E30" t="str">
-        <v>No</v>
-      </c>
-      <c r="K30" t="str">
-        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
-      </c>
-      <c r="W30" t="str">
+        <v>No disponible</v>
+      </c>
+      <c r="F30" t="str">
+        <v>No</v>
+      </c>
+      <c r="H30" t="str">
+        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
+      </c>
+      <c r="I30" t="str">
         <v>https://1fichier.com/?uu8dpozdsw6uyzchkkvo</v>
       </c>
-      <c r="AK30" t="str">
+      <c r="N30" t="str">
         <v>https://downloadgameps3.net/archives/9737</v>
       </c>
-      <c r="AL30" t="str">
-        <v>https://gamepciso.com/</v>
-      </c>
-      <c r="AM30" t="str">
-        <v>https://downloadgameps3.net/archives/18667</v>
-      </c>
-      <c r="AN30" t="str">
+      <c r="O30" t="str">
+        <v>https://gamepciso.com/</v>
+      </c>
+      <c r="P30" t="str">
+        <v>https://downloadgameps3.net/archives/18667</v>
+      </c>
+      <c r="Q30" t="str">
         <v>https://dlpsgame.com/guide-jdownloader-2/</v>
       </c>
     </row>
@@ -1920,27 +1600,24 @@
         <v>imagenes/PS3/Solitaire PSN.jpg</v>
       </c>
       <c r="E31" t="str">
-        <v>No</v>
-      </c>
-      <c r="K31" t="str">
-        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
-      </c>
-      <c r="X31" t="str">
-        <v>https://1fichier.com/?u3640symul9s59wif25t</v>
-      </c>
-      <c r="Y31" t="str">
-        <v>https://1fichier.com/?ulvf6mfl37</v>
-      </c>
-      <c r="AK31" t="str">
+        <v>No disponible</v>
+      </c>
+      <c r="F31" t="str">
+        <v>No</v>
+      </c>
+      <c r="H31" t="str">
+        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
+      </c>
+      <c r="N31" t="str">
         <v>https://downloadgameps3.net/archives/21277</v>
       </c>
-      <c r="AL31" t="str">
-        <v>https://gamepciso.com/</v>
-      </c>
-      <c r="AM31" t="str">
-        <v>https://downloadgameps3.net/archives/18667</v>
-      </c>
-      <c r="AN31" t="str">
+      <c r="O31" t="str">
+        <v>https://gamepciso.com/</v>
+      </c>
+      <c r="P31" t="str">
+        <v>https://downloadgameps3.net/archives/18667</v>
+      </c>
+      <c r="Q31" t="str">
         <v>https://dlpsgame.com/guide-jdownloader-2/</v>
       </c>
     </row>
@@ -1958,24 +1635,27 @@
         <v>imagenes/PS3/Motorbike Racing Pack.jpg</v>
       </c>
       <c r="E32" t="str">
-        <v>No</v>
-      </c>
-      <c r="K32" t="str">
-        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
-      </c>
-      <c r="W32" t="str">
+        <v>No disponible</v>
+      </c>
+      <c r="F32" t="str">
+        <v>No</v>
+      </c>
+      <c r="H32" t="str">
+        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
+      </c>
+      <c r="I32" t="str">
         <v>https://1fichier.com/?5j9zb3g3dk5vtnbdcs3i</v>
       </c>
-      <c r="AK32" t="str">
+      <c r="N32" t="str">
         <v>https://downloadgameps3.net/archives/10803</v>
       </c>
-      <c r="AL32" t="str">
-        <v>https://gamepciso.com/</v>
-      </c>
-      <c r="AM32" t="str">
-        <v>https://downloadgameps3.net/archives/18667</v>
-      </c>
-      <c r="AN32" t="str">
+      <c r="O32" t="str">
+        <v>https://gamepciso.com/</v>
+      </c>
+      <c r="P32" t="str">
+        <v>https://downloadgameps3.net/archives/18667</v>
+      </c>
+      <c r="Q32" t="str">
         <v>https://dlpsgame.com/guide-jdownloader-2/</v>
       </c>
     </row>
@@ -1993,48 +1673,30 @@
         <v>imagenes/PS3/The Legend of Heroes Trails of Cold Steel 2.jpg</v>
       </c>
       <c r="E33" t="str">
-        <v>No</v>
-      </c>
-      <c r="G33" t="str">
-        <v>https://filecrypt.cc/Container/CAA7B8C99D.html</v>
-      </c>
-      <c r="H33" t="str">
-        <v>https://goo.gl/h9bs4M</v>
-      </c>
-      <c r="I33" t="str">
-        <v>https://mega.nz/#!EsBASQbC!0sV6NjXDkKYoxdDnfUmKSMtvylJU-nQSehjtbf_dnaU</v>
-      </c>
-      <c r="L33" t="str">
-        <v>https://filecrypt.cc/Container/EB8567AD6C.html</v>
-      </c>
-      <c r="M33" t="str">
-        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
-      </c>
-      <c r="X33" t="str">
-        <v>https://1fichier.com/?37h5ubqvd6wh4tqkxnqp</v>
-      </c>
-      <c r="Y33" t="str">
-        <v>https://1fichier.com/?1dhtc4qaf28khn3cjkpw</v>
-      </c>
-      <c r="AK33" t="str">
+        <v>No disponible</v>
+      </c>
+      <c r="F33" t="str">
+        <v>No</v>
+      </c>
+      <c r="N33" t="str">
         <v>https://downloadgameps3.net/archives/10267</v>
       </c>
-      <c r="AL33" t="str">
+      <c r="O33" t="str">
         <v>https://downloadgameps3.net/archives/10265</v>
       </c>
-      <c r="AM33" t="str">
+      <c r="P33" t="str">
         <v>https://downloadgameps3.net/archives/9174</v>
       </c>
-      <c r="AN33" t="str">
+      <c r="Q33" t="str">
         <v>https://goo.gl/RBUZGp</v>
       </c>
-      <c r="AO33" t="str">
-        <v>https://gamepciso.com/</v>
-      </c>
-      <c r="AP33" t="str">
-        <v>https://downloadgameps3.net/archives/18667</v>
-      </c>
-      <c r="AQ33" t="str">
+      <c r="R33" t="str">
+        <v>https://gamepciso.com/</v>
+      </c>
+      <c r="S33" t="str">
+        <v>https://downloadgameps3.net/archives/18667</v>
+      </c>
+      <c r="T33" t="str">
         <v>https://dlpsgame.com/guide-jdownloader-2/</v>
       </c>
     </row>
@@ -2052,30 +1714,27 @@
         <v>imagenes/PS3/Just Dance 2017.jpg</v>
       </c>
       <c r="E34" t="str">
-        <v>No</v>
-      </c>
-      <c r="K34" t="str">
-        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
-      </c>
-      <c r="X34" t="str">
-        <v>https://1fichier.com/?fm3ncpg6l3n2yyfggekv</v>
-      </c>
-      <c r="Y34" t="str">
-        <v>https://1fichier.com/?at1pjtkour7ufitzcjpm</v>
-      </c>
-      <c r="AK34" t="str">
+        <v>No disponible</v>
+      </c>
+      <c r="F34" t="str">
+        <v>No</v>
+      </c>
+      <c r="H34" t="str">
+        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
+      </c>
+      <c r="N34" t="str">
         <v>https://downloadgameps3.net/archives/10092</v>
       </c>
-      <c r="AL34" t="str">
+      <c r="O34" t="str">
         <v>https://downloadgameps3.net/archives/10094</v>
       </c>
-      <c r="AM34" t="str">
-        <v>https://gamepciso.com/</v>
-      </c>
-      <c r="AN34" t="str">
-        <v>https://downloadgameps3.net/archives/18667</v>
-      </c>
-      <c r="AO34" t="str">
+      <c r="P34" t="str">
+        <v>https://gamepciso.com/</v>
+      </c>
+      <c r="Q34" t="str">
+        <v>https://downloadgameps3.net/archives/18667</v>
+      </c>
+      <c r="R34" t="str">
         <v>https://dlpsgame.com/guide-jdownloader-2/</v>
       </c>
     </row>
@@ -2093,48 +1752,42 @@
         <v>imagenes/PS3/Blazblue Central Fiction.jpg</v>
       </c>
       <c r="E35" t="str">
-        <v>No</v>
+        <v>No disponible</v>
       </c>
       <c r="F35" t="str">
+        <v>No</v>
+      </c>
+      <c r="G35" t="str">
         <v>https://mega.nz/#F!mZYGEQzD!iIn3BU3j5MAMpfUDTW7YzQ</v>
       </c>
-      <c r="K35" t="str">
-        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
-      </c>
-      <c r="X35" t="str">
-        <v>https://1fichier.com/?jvmwwtte9hyjsxrpe7d2</v>
-      </c>
-      <c r="Y35" t="str">
-        <v>https://1fichier.com/?afmr2p44no68fy017ksr</v>
-      </c>
-      <c r="Z35" t="str">
-        <v>https://1fichier.com/?y4wgikuxdo537486rfj8</v>
-      </c>
-      <c r="AK35" t="str">
+      <c r="H35" t="str">
+        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
+      </c>
+      <c r="N35" t="str">
         <v>https://downloadgameps3.net/archives/8135</v>
       </c>
-      <c r="AL35" t="str">
+      <c r="O35" t="str">
         <v>https://anotepad.com/notes/d8x2jn8a</v>
       </c>
-      <c r="AM35" t="str">
+      <c r="P35" t="str">
         <v>https://downloadgameps3.net/archives/8137</v>
       </c>
-      <c r="AN35" t="str">
+      <c r="Q35" t="str">
         <v>https://downloadgameps3.net/archives/8139</v>
       </c>
-      <c r="AO35" t="str">
+      <c r="R35" t="str">
         <v>https://anotepad.com/notes/xa4wh4p8</v>
       </c>
-      <c r="AP35" t="str">
+      <c r="S35" t="str">
         <v>https://anotepad.com/notes/92ww8wer</v>
       </c>
-      <c r="AQ35" t="str">
-        <v>https://gamepciso.com/</v>
-      </c>
-      <c r="AR35" t="str">
-        <v>https://downloadgameps3.net/archives/18667</v>
-      </c>
-      <c r="AS35" t="str">
+      <c r="T35" t="str">
+        <v>https://gamepciso.com/</v>
+      </c>
+      <c r="U35" t="str">
+        <v>https://downloadgameps3.net/archives/18667</v>
+      </c>
+      <c r="V35" t="str">
         <v>https://dlpsgame.com/guide-jdownloader-2/</v>
       </c>
     </row>
@@ -2152,36 +1805,27 @@
         <v>imagenes/PS3/Minecraft Story Mode A Telltale Games Series The C.jpg</v>
       </c>
       <c r="E36" t="str">
-        <v>No</v>
-      </c>
-      <c r="G36" t="str">
-        <v>https://filecrypt.cc/Container/748890DC37.html</v>
-      </c>
-      <c r="H36" t="str">
-        <v>https://filecrypt.cc/Container/0A9AF20673.html</v>
-      </c>
-      <c r="L36" t="str">
-        <v>https://filecrypt.cc/Container/8AB1C28BD8.html</v>
-      </c>
-      <c r="M36" t="str">
-        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
-      </c>
-      <c r="W36" t="str">
+        <v>No disponible</v>
+      </c>
+      <c r="F36" t="str">
+        <v>No</v>
+      </c>
+      <c r="I36" t="str">
         <v>https://1fichier.com/?i0n5dsdvsi5ecbcw6f6s</v>
       </c>
-      <c r="AK36" t="str">
+      <c r="N36" t="str">
         <v>https://downloadgameps3.net/archives/10672</v>
       </c>
-      <c r="AL36" t="str">
+      <c r="O36" t="str">
         <v>https://downloadgameps3.net/archives/10675</v>
       </c>
-      <c r="AM36" t="str">
-        <v>https://gamepciso.com/</v>
-      </c>
-      <c r="AN36" t="str">
-        <v>https://downloadgameps3.net/archives/18667</v>
-      </c>
-      <c r="AO36" t="str">
+      <c r="P36" t="str">
+        <v>https://gamepciso.com/</v>
+      </c>
+      <c r="Q36" t="str">
+        <v>https://downloadgameps3.net/archives/18667</v>
+      </c>
+      <c r="R36" t="str">
         <v>https://dlpsgame.com/guide-jdownloader-2/</v>
       </c>
     </row>
@@ -2199,42 +1843,45 @@
         <v>imagenes/PS3/Batman The Telltale Series [Episode 1-5].jpg</v>
       </c>
       <c r="E37" t="str">
-        <v>No</v>
-      </c>
-      <c r="K37" t="str">
-        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
-      </c>
-      <c r="AK37" t="str">
+        <v>No disponible</v>
+      </c>
+      <c r="F37" t="str">
+        <v>No</v>
+      </c>
+      <c r="H37" t="str">
+        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
+      </c>
+      <c r="N37" t="str">
         <v>https://goo.gl/zrQwyQ</v>
       </c>
-      <c r="AL37" t="str">
+      <c r="O37" t="str">
         <v>http://zeus.dl.playstation.net/cdn/UP2026/NPUB31845_00/UP2026-NPUB31845_00-BATM000000000EP2_bg_1_385052a4b1e4d486cb36f5bab6b5cdc833cb0f27.pkg</v>
       </c>
-      <c r="AM37" t="str">
+      <c r="P37" t="str">
         <v>http://zeus.dl.playstation.net/cdn/UP2026/NPUB31845_00/UP2026-NPUB31845_00-BATM000000000EP3_bg_2_9f69a5d1f4e3f6d70a342926b49ccad9e3ec77b4.pkg</v>
       </c>
-      <c r="AN37" t="str">
+      <c r="Q37" t="str">
         <v>https://goo.gl/RfpVL4</v>
       </c>
-      <c r="AO37" t="str">
+      <c r="R37" t="str">
         <v>http://zeus.dl.playstation.net/cdn/UP2026/NPUB31845_00/UP2026-NPUB31845_00-BATM000000000EP5_bg_1_e929b1a053b695e3035543c85dd6f93ce3032e21.pkg</v>
       </c>
-      <c r="AP37" t="str">
+      <c r="S37" t="str">
         <v>http://b0.ww.np.dl.playstation.net/tppkg/np/NPUB31845/NPUB31845_T3/cbfdae88669c59c6/UP2026-NPUB31845_00-BATM000000000EP1-A0104-V0100-PE.pkg</v>
       </c>
-      <c r="AQ37" t="str">
+      <c r="T37" t="str">
         <v>http://b0.ww.np.dl.playstation.net/tppkg/np/NPUB31845/NPUB31845_T4/181a15b646c70a32/UP2026-NPUB31845_00-BATM000000000EP1-A0105-V0101-PE.pkg</v>
       </c>
-      <c r="AR37" t="str">
+      <c r="U37" t="str">
         <v>https://anotepad.com/notes/9k28283c</v>
       </c>
-      <c r="AS37" t="str">
-        <v>https://gamepciso.com/</v>
-      </c>
-      <c r="AT37" t="str">
-        <v>https://downloadgameps3.net/archives/18667</v>
-      </c>
-      <c r="AU37" t="str">
+      <c r="V37" t="str">
+        <v>https://gamepciso.com/</v>
+      </c>
+      <c r="W37" t="str">
+        <v>https://downloadgameps3.net/archives/18667</v>
+      </c>
+      <c r="X37" t="str">
         <v>https://dlpsgame.com/guide-jdownloader-2/</v>
       </c>
     </row>
@@ -2252,54 +1899,33 @@
         <v>imagenes/PS3/WWE 2K17.jpg</v>
       </c>
       <c r="E38" t="str">
-        <v>No</v>
-      </c>
-      <c r="G38" t="str">
-        <v>https://goo.gl/8UmzEh</v>
-      </c>
-      <c r="H38" t="str">
-        <v>https://filecrypt.cc/Container/83D6CBBF7F.html</v>
-      </c>
-      <c r="I38" t="str">
-        <v>https://filecrypt.cc/Container/D87DCDF9BE.html</v>
-      </c>
-      <c r="L38" t="str">
-        <v>https://filecrypt.cc/Container/7AD2774AA7.html</v>
-      </c>
-      <c r="M38" t="str">
-        <v>https://filecrypt.cc/Container/A3CD0D95C2.html</v>
+        <v>No disponible</v>
+      </c>
+      <c r="F38" t="str">
+        <v>No</v>
       </c>
       <c r="N38" t="str">
-        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
-      </c>
-      <c r="X38" t="str">
-        <v>https://1fichier.com/?1kgsbsxp8x7zhpyzzjlh</v>
-      </c>
-      <c r="Y38" t="str">
-        <v>https://filecrypt.cc/Container/02C33BB23C.html</v>
-      </c>
-      <c r="AK38" t="str">
         <v>https://downloadgameps3.net/archives/12856</v>
       </c>
-      <c r="AL38" t="str">
+      <c r="O38" t="str">
         <v>https://downloadgameps3.net/archives/14985</v>
       </c>
-      <c r="AM38" t="str">
+      <c r="P38" t="str">
         <v>https://downloadgameps3.net/archives/12854</v>
       </c>
-      <c r="AN38" t="str">
+      <c r="Q38" t="str">
         <v>https://downloadgameps3.net/archives/14987</v>
       </c>
-      <c r="AO38" t="str">
+      <c r="R38" t="str">
         <v>https://downloadgameps3.net/archives/5834</v>
       </c>
-      <c r="AP38" t="str">
-        <v>https://gamepciso.com/</v>
-      </c>
-      <c r="AQ38" t="str">
-        <v>https://downloadgameps3.net/archives/18667</v>
-      </c>
-      <c r="AR38" t="str">
+      <c r="S38" t="str">
+        <v>https://gamepciso.com/</v>
+      </c>
+      <c r="T38" t="str">
+        <v>https://downloadgameps3.net/archives/18667</v>
+      </c>
+      <c r="U38" t="str">
         <v>https://dlpsgame.com/guide-jdownloader-2/</v>
       </c>
     </row>
@@ -2317,30 +1943,27 @@
         <v>imagenes/PS3/LEGO Marvels Avengers.jpg</v>
       </c>
       <c r="E39" t="str">
-        <v>No</v>
-      </c>
-      <c r="K39" t="str">
-        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
-      </c>
-      <c r="X39" t="str">
-        <v>https://1fichier.com/?746g7affwgws8fmyt666</v>
-      </c>
-      <c r="Y39" t="str">
-        <v>https://1fichier.com/?y9uyn0kvg6bpwaajqjst</v>
-      </c>
-      <c r="AK39" t="str">
+        <v>No disponible</v>
+      </c>
+      <c r="F39" t="str">
+        <v>No</v>
+      </c>
+      <c r="H39" t="str">
+        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
+      </c>
+      <c r="N39" t="str">
         <v>https://anotepad.com/notes/tsbhn6b5</v>
       </c>
-      <c r="AL39" t="str">
+      <c r="O39" t="str">
         <v>https://anotepad.com/notes/rbpfmrx4</v>
       </c>
-      <c r="AM39" t="str">
-        <v>https://gamepciso.com/</v>
-      </c>
-      <c r="AN39" t="str">
-        <v>https://downloadgameps3.net/archives/18667</v>
-      </c>
-      <c r="AO39" t="str">
+      <c r="P39" t="str">
+        <v>https://gamepciso.com/</v>
+      </c>
+      <c r="Q39" t="str">
+        <v>https://downloadgameps3.net/archives/18667</v>
+      </c>
+      <c r="R39" t="str">
         <v>https://dlpsgame.com/guide-jdownloader-2/</v>
       </c>
     </row>
@@ -2358,51 +1981,33 @@
         <v>imagenes/PS3/FIFA 17.jpg</v>
       </c>
       <c r="E40" t="str">
-        <v>No</v>
-      </c>
-      <c r="G40" t="str">
-        <v>https://filecrypt.cc/Container/B391F88D11.html</v>
-      </c>
-      <c r="H40" t="str">
-        <v>https://filecrypt.cc/Container/F99426ABD6.html</v>
-      </c>
-      <c r="L40" t="str">
-        <v>https://filecrypt.cc/Container/8500FE984F.html</v>
-      </c>
-      <c r="M40" t="str">
-        <v>https://filecrypt.cc/Container/4ACA78FF9C.html</v>
+        <v>No disponible</v>
+      </c>
+      <c r="F40" t="str">
+        <v>No</v>
       </c>
       <c r="N40" t="str">
-        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
-      </c>
-      <c r="X40" t="str">
-        <v>https://1fichier.com/?tbrqi0o5p10pxx69oczs</v>
-      </c>
-      <c r="Y40" t="str">
-        <v>https://1fichier.com/?yscikzmzqxyqtyhy2s10</v>
-      </c>
-      <c r="AK40" t="str">
         <v>https://downloadgameps3.net/archives/9376</v>
       </c>
-      <c r="AL40" t="str">
+      <c r="O40" t="str">
         <v>https://downloadgameps3.net/archives/9378</v>
       </c>
-      <c r="AM40" t="str">
+      <c r="P40" t="str">
         <v>https://anotepad.com/notes/adym4eky</v>
       </c>
-      <c r="AN40" t="str">
+      <c r="Q40" t="str">
         <v>https://anotepad.com/notes/nt34h6ye</v>
       </c>
-      <c r="AO40" t="str">
-        <v>https://downloadgameps3.net/archives/18667</v>
-      </c>
-      <c r="AP40" t="str">
+      <c r="R40" t="str">
+        <v>https://downloadgameps3.net/archives/18667</v>
+      </c>
+      <c r="S40" t="str">
         <v>https://dlpsgame.com/guide-download-game-use-jdownload/</v>
       </c>
-      <c r="AQ40" t="str">
-        <v>https://gamepciso.com/</v>
-      </c>
-      <c r="AR40" t="str">
+      <c r="T40" t="str">
+        <v>https://gamepciso.com/</v>
+      </c>
+      <c r="U40" t="str">
         <v>https://dlpsgame.com/guide-jdownloader-2/</v>
       </c>
     </row>
@@ -2420,21 +2025,24 @@
         <v>imagenes/PS3/Sky Force Anniversary PSN.jpg</v>
       </c>
       <c r="E41" t="str">
-        <v>No</v>
+        <v>No disponible</v>
       </c>
       <c r="F41" t="str">
+        <v>No</v>
+      </c>
+      <c r="G41" t="str">
         <v>https://goo.gl/fsVs0p</v>
       </c>
-      <c r="K41" t="str">
-        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
-      </c>
-      <c r="AK41" t="str">
-        <v>https://gamepciso.com/</v>
-      </c>
-      <c r="AL41" t="str">
-        <v>https://downloadgameps3.net/archives/18667</v>
-      </c>
-      <c r="AM41" t="str">
+      <c r="H41" t="str">
+        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
+      </c>
+      <c r="N41" t="str">
+        <v>https://gamepciso.com/</v>
+      </c>
+      <c r="O41" t="str">
+        <v>https://downloadgameps3.net/archives/18667</v>
+      </c>
+      <c r="P41" t="str">
         <v>https://dlpsgame.com/guide-jdownloader-2/</v>
       </c>
     </row>
@@ -2452,21 +2060,24 @@
         <v>imagenes/PS3/Amplitude PSN.jpg</v>
       </c>
       <c r="E42" t="str">
-        <v>No</v>
+        <v>No disponible</v>
       </c>
       <c r="F42" t="str">
+        <v>No</v>
+      </c>
+      <c r="G42" t="str">
         <v>https://filecrypt.cc/Container/48EDB39DF1.html</v>
       </c>
-      <c r="K42" t="str">
-        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
-      </c>
-      <c r="AK42" t="str">
-        <v>https://gamepciso.com/</v>
-      </c>
-      <c r="AL42" t="str">
-        <v>https://downloadgameps3.net/archives/18667</v>
-      </c>
-      <c r="AM42" t="str">
+      <c r="H42" t="str">
+        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
+      </c>
+      <c r="N42" t="str">
+        <v>https://gamepciso.com/</v>
+      </c>
+      <c r="O42" t="str">
+        <v>https://downloadgameps3.net/archives/18667</v>
+      </c>
+      <c r="P42" t="str">
         <v>https://dlpsgame.com/guide-jdownloader-2/</v>
       </c>
     </row>
@@ -2484,27 +2095,24 @@
         <v>imagenes/PS3/Brick Breaker PSN.jpg</v>
       </c>
       <c r="E43" t="str">
-        <v>No</v>
-      </c>
-      <c r="K43" t="str">
-        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
-      </c>
-      <c r="X43" t="str">
-        <v>https://1fichier.com/?yvw646f2dj70jycxpyah</v>
-      </c>
-      <c r="Y43" t="str">
-        <v>https://1fichier.com/?i0mytbq7lu</v>
-      </c>
-      <c r="AK43" t="str">
+        <v>No disponible</v>
+      </c>
+      <c r="F43" t="str">
+        <v>No</v>
+      </c>
+      <c r="H43" t="str">
+        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
+      </c>
+      <c r="N43" t="str">
         <v>https://downloadgameps3.net/archives/19589</v>
       </c>
-      <c r="AL43" t="str">
-        <v>https://gamepciso.com/</v>
-      </c>
-      <c r="AM43" t="str">
-        <v>https://downloadgameps3.net/archives/18667</v>
-      </c>
-      <c r="AN43" t="str">
+      <c r="O43" t="str">
+        <v>https://gamepciso.com/</v>
+      </c>
+      <c r="P43" t="str">
+        <v>https://downloadgameps3.net/archives/18667</v>
+      </c>
+      <c r="Q43" t="str">
         <v>https://dlpsgame.com/guide-jdownloader-2/</v>
       </c>
     </row>
@@ -2522,27 +2130,24 @@
         <v>imagenes/PS3/BreakQuest Extra Evolution PSN.jpg</v>
       </c>
       <c r="E44" t="str">
-        <v>No</v>
-      </c>
-      <c r="K44" t="str">
-        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
-      </c>
-      <c r="X44" t="str">
-        <v>https://1fichier.com/?qxd5tjqrlpxsmmet911g</v>
-      </c>
-      <c r="Y44" t="str">
-        <v>https://1fichier.com/?mzzl3e7syj</v>
-      </c>
-      <c r="AK44" t="str">
+        <v>No disponible</v>
+      </c>
+      <c r="F44" t="str">
+        <v>No</v>
+      </c>
+      <c r="H44" t="str">
+        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
+      </c>
+      <c r="N44" t="str">
         <v>https://downloadgameps3.net/archives/19583</v>
       </c>
-      <c r="AL44" t="str">
-        <v>https://gamepciso.com/</v>
-      </c>
-      <c r="AM44" t="str">
-        <v>https://downloadgameps3.net/archives/18667</v>
-      </c>
-      <c r="AN44" t="str">
+      <c r="O44" t="str">
+        <v>https://gamepciso.com/</v>
+      </c>
+      <c r="P44" t="str">
+        <v>https://downloadgameps3.net/archives/18667</v>
+      </c>
+      <c r="Q44" t="str">
         <v>https://dlpsgame.com/guide-jdownloader-2/</v>
       </c>
     </row>
@@ -2560,36 +2165,33 @@
         <v>imagenes/PS3/NBA 2K17.jpg</v>
       </c>
       <c r="E45" t="str">
-        <v>No</v>
+        <v>No disponible</v>
       </c>
       <c r="F45" t="str">
+        <v>No</v>
+      </c>
+      <c r="G45" t="str">
         <v>https://filecrypt.cc/Container/59BCB6D784.html</v>
       </c>
-      <c r="L45" t="str">
-        <v>https://filecrypt.cc/Container/5C666EFA5F.html</v>
-      </c>
-      <c r="M45" t="str">
-        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
-      </c>
-      <c r="W45" t="str">
+      <c r="I45" t="str">
         <v>https://1fichier.com/?zye43hwtc0prhc4q9thj</v>
       </c>
-      <c r="AK45" t="str">
+      <c r="N45" t="str">
         <v>https://downloadgameps3.net/archives/10950</v>
       </c>
-      <c r="AL45" t="str">
+      <c r="O45" t="str">
         <v>https://anotepad.com/notes/94aj5fh7</v>
       </c>
-      <c r="AM45" t="str">
+      <c r="P45" t="str">
         <v>https://downloadgameps3.net/archives/10952</v>
       </c>
-      <c r="AN45" t="str">
-        <v>https://gamepciso.com/</v>
-      </c>
-      <c r="AO45" t="str">
-        <v>https://downloadgameps3.net/archives/18667</v>
-      </c>
-      <c r="AP45" t="str">
+      <c r="Q45" t="str">
+        <v>https://gamepciso.com/</v>
+      </c>
+      <c r="R45" t="str">
+        <v>https://downloadgameps3.net/archives/18667</v>
+      </c>
+      <c r="S45" t="str">
         <v>https://dlpsgame.com/guide-jdownloader-2/</v>
       </c>
     </row>
@@ -2607,54 +2209,27 @@
         <v>imagenes/PS3/Pro Evolution Soccer 2017 [PES 2017].jpg</v>
       </c>
       <c r="E46" t="str">
-        <v>No</v>
-      </c>
-      <c r="G46" t="str">
-        <v>https://filecrypt.cc/Container/12568F205F.html</v>
-      </c>
-      <c r="H46" t="str">
-        <v>https://filecrypt.cc/Container/5DEB4C6ECD.html</v>
-      </c>
-      <c r="I46" t="str">
-        <v>https://mega.nz/#!Qto1WLDA!y_j-gGd4L1BP0PLBKZJHMbO-2eEQOTmm_j1_O7qrJqw</v>
-      </c>
-      <c r="L46" t="str">
-        <v>https://filecrypt.cc/Container/9FC4772753.html</v>
-      </c>
-      <c r="M46" t="str">
-        <v>http://www.mediafire.com/file/tscrfsomrha9i4d/Pes2017+OF+Bles+and+Blus+PS3.rar</v>
+        <v>No disponible</v>
+      </c>
+      <c r="F46" t="str">
+        <v>No</v>
       </c>
       <c r="N46" t="str">
-        <v>https://filecrypt.cc/Container/8967E65D5F.html</v>
+        <v>https://downloadgameps3.net/archives/11246</v>
       </c>
       <c r="O46" t="str">
-        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
-      </c>
-      <c r="X46" t="str">
-        <v>https://1fichier.com/?j5i6g6sv6fede5t6venx</v>
-      </c>
-      <c r="Y46" t="str">
-        <v>https://1fichier.com/?68lmb7xok4xpwwoxhql6</v>
-      </c>
-      <c r="Z46" t="str">
-        <v>https://1fichier.com/?ag8r54h0zaggpd9hhc0d</v>
-      </c>
-      <c r="AK46" t="str">
-        <v>https://downloadgameps3.net/archives/11246</v>
-      </c>
-      <c r="AL46" t="str">
         <v>https://downloadgameps3.net/archives/11248</v>
       </c>
-      <c r="AM46" t="str">
+      <c r="P46" t="str">
         <v>https://goo.gl/7LcmjM</v>
       </c>
-      <c r="AN46" t="str">
-        <v>https://gamepciso.com/</v>
-      </c>
-      <c r="AO46" t="str">
-        <v>https://downloadgameps3.net/archives/18667</v>
-      </c>
-      <c r="AP46" t="str">
+      <c r="Q46" t="str">
+        <v>https://gamepciso.com/</v>
+      </c>
+      <c r="R46" t="str">
+        <v>https://downloadgameps3.net/archives/18667</v>
+      </c>
+      <c r="S46" t="str">
         <v>https://dlpsgame.com/guide-jdownloader-2/</v>
       </c>
     </row>
@@ -2672,24 +2247,27 @@
         <v>imagenes/PS3/Attack on Titan Wings of Freedom.jpg</v>
       </c>
       <c r="E47" t="str">
-        <v>No</v>
+        <v>No disponible</v>
       </c>
       <c r="F47" t="str">
+        <v>No</v>
+      </c>
+      <c r="G47" t="str">
         <v>https://goo.gl/j2ZtJc</v>
       </c>
-      <c r="K47" t="str">
-        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
-      </c>
-      <c r="AK47" t="str">
+      <c r="H47" t="str">
+        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
+      </c>
+      <c r="N47" t="str">
         <v>https://downloadgameps3.net/archives/12991</v>
       </c>
-      <c r="AL47" t="str">
-        <v>https://gamepciso.com/</v>
-      </c>
-      <c r="AM47" t="str">
-        <v>https://downloadgameps3.net/archives/18667</v>
-      </c>
-      <c r="AN47" t="str">
+      <c r="O47" t="str">
+        <v>https://gamepciso.com/</v>
+      </c>
+      <c r="P47" t="str">
+        <v>https://downloadgameps3.net/archives/18667</v>
+      </c>
+      <c r="Q47" t="str">
         <v>https://dlpsgame.com/guide-jdownloader-2/</v>
       </c>
     </row>
@@ -2707,24 +2285,27 @@
         <v>imagenes/PS3/Sengoku Basara Sanada Yukimura den.jpg</v>
       </c>
       <c r="E48" t="str">
-        <v>No</v>
+        <v>No disponible</v>
       </c>
       <c r="F48" t="str">
+        <v>No</v>
+      </c>
+      <c r="G48" t="str">
         <v>https://filecrypt.cc/Container/2DE781E091.html</v>
       </c>
-      <c r="K48" t="str">
-        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
-      </c>
-      <c r="AK48" t="str">
+      <c r="H48" t="str">
+        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
+      </c>
+      <c r="N48" t="str">
         <v>https://downloadgameps3.net/archives/11758</v>
       </c>
-      <c r="AL48" t="str">
-        <v>https://gamepciso.com/</v>
-      </c>
-      <c r="AM48" t="str">
-        <v>https://downloadgameps3.net/archives/18667</v>
-      </c>
-      <c r="AN48" t="str">
+      <c r="O48" t="str">
+        <v>https://gamepciso.com/</v>
+      </c>
+      <c r="P48" t="str">
+        <v>https://downloadgameps3.net/archives/18667</v>
+      </c>
+      <c r="Q48" t="str">
         <v>https://dlpsgame.com/guide-jdownloader-2/</v>
       </c>
     </row>
@@ -2742,24 +2323,27 @@
         <v>imagenes/PS3/Shin Sangoku Musou Eiketsuden.jpg</v>
       </c>
       <c r="E49" t="str">
-        <v>No</v>
-      </c>
-      <c r="K49" t="str">
-        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
-      </c>
-      <c r="W49" t="str">
+        <v>No disponible</v>
+      </c>
+      <c r="F49" t="str">
+        <v>No</v>
+      </c>
+      <c r="H49" t="str">
+        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
+      </c>
+      <c r="I49" t="str">
         <v>https://1fichier.com/?nwaiaie5i1bvl89hchuj</v>
       </c>
-      <c r="AK49" t="str">
+      <c r="N49" t="str">
         <v>https://downloadgameps3.net/archives/11829</v>
       </c>
-      <c r="AL49" t="str">
-        <v>https://gamepciso.com/</v>
-      </c>
-      <c r="AM49" t="str">
-        <v>https://downloadgameps3.net/archives/18667</v>
-      </c>
-      <c r="AN49" t="str">
+      <c r="O49" t="str">
+        <v>https://gamepciso.com/</v>
+      </c>
+      <c r="P49" t="str">
+        <v>https://downloadgameps3.net/archives/18667</v>
+      </c>
+      <c r="Q49" t="str">
         <v>https://dlpsgame.com/guide-jdownloader-2/</v>
       </c>
     </row>
@@ -2777,36 +2361,27 @@
         <v>imagenes/PS3/Madden NFL 17.jpg</v>
       </c>
       <c r="E50" t="str">
-        <v>No</v>
-      </c>
-      <c r="G50" t="str">
-        <v>https://goo.gl/senuSN</v>
-      </c>
-      <c r="H50" t="str">
-        <v>https://filecrypt.cc/Container/744885E02F.html</v>
-      </c>
-      <c r="L50" t="str">
-        <v>https://filecrypt.cc/Container/05051D0520.html</v>
-      </c>
-      <c r="M50" t="str">
-        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
-      </c>
-      <c r="W50" t="str">
+        <v>No disponible</v>
+      </c>
+      <c r="F50" t="str">
+        <v>No</v>
+      </c>
+      <c r="I50" t="str">
         <v>https://1fichier.com/?2qxv2qz2bjo6tffs7xx5</v>
       </c>
-      <c r="AK50" t="str">
+      <c r="N50" t="str">
         <v>https://downloadgameps3.net/archives/10470</v>
       </c>
-      <c r="AL50" t="str">
+      <c r="O50" t="str">
         <v>https://downloadgameps3.net/archives/10472</v>
       </c>
-      <c r="AM50" t="str">
-        <v>https://gamepciso.com/</v>
-      </c>
-      <c r="AN50" t="str">
-        <v>https://downloadgameps3.net/archives/18667</v>
-      </c>
-      <c r="AO50" t="str">
+      <c r="P50" t="str">
+        <v>https://gamepciso.com/</v>
+      </c>
+      <c r="Q50" t="str">
+        <v>https://downloadgameps3.net/archives/18667</v>
+      </c>
+      <c r="R50" t="str">
         <v>https://dlpsgame.com/guide-jdownloader-2/</v>
       </c>
     </row>
@@ -2824,24 +2399,27 @@
         <v>imagenes/PS3/Root Double Before Crime After Days Xtend Edition.jpg</v>
       </c>
       <c r="E51" t="str">
-        <v>No</v>
-      </c>
-      <c r="K51" t="str">
-        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
-      </c>
-      <c r="W51" t="str">
+        <v>No disponible</v>
+      </c>
+      <c r="F51" t="str">
+        <v>No</v>
+      </c>
+      <c r="H51" t="str">
+        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
+      </c>
+      <c r="I51" t="str">
         <v>https://1fichier.com/?gn5zwxv6nx12gam46o45</v>
       </c>
-      <c r="AK51" t="str">
+      <c r="N51" t="str">
         <v>https://downloadgameps3.net/archives/11625</v>
       </c>
-      <c r="AL51" t="str">
-        <v>https://gamepciso.com/</v>
-      </c>
-      <c r="AM51" t="str">
-        <v>https://downloadgameps3.net/archives/18667</v>
-      </c>
-      <c r="AN51" t="str">
+      <c r="O51" t="str">
+        <v>https://gamepciso.com/</v>
+      </c>
+      <c r="P51" t="str">
+        <v>https://downloadgameps3.net/archives/18667</v>
+      </c>
+      <c r="Q51" t="str">
         <v>https://dlpsgame.com/guide-jdownloader-2/</v>
       </c>
     </row>
@@ -2859,27 +2437,30 @@
         <v>imagenes/PS3/Shin Hayarigami 2.jpg</v>
       </c>
       <c r="E52" t="str">
-        <v>No</v>
+        <v>No disponible</v>
       </c>
       <c r="F52" t="str">
+        <v>No</v>
+      </c>
+      <c r="G52" t="str">
         <v>https://goo.gl/4K064M</v>
       </c>
-      <c r="K52" t="str">
-        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
-      </c>
-      <c r="W52" t="str">
+      <c r="H52" t="str">
+        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
+      </c>
+      <c r="I52" t="str">
         <v>https://1fichier.com/?4k30f5501z43khpxlvy7</v>
       </c>
-      <c r="AK52" t="str">
+      <c r="N52" t="str">
         <v>https://downloadgameps3.net/archives/11819</v>
       </c>
-      <c r="AL52" t="str">
-        <v>https://gamepciso.com/</v>
-      </c>
-      <c r="AM52" t="str">
-        <v>https://downloadgameps3.net/archives/18667</v>
-      </c>
-      <c r="AN52" t="str">
+      <c r="O52" t="str">
+        <v>https://gamepciso.com/</v>
+      </c>
+      <c r="P52" t="str">
+        <v>https://downloadgameps3.net/archives/18667</v>
+      </c>
+      <c r="Q52" t="str">
         <v>https://dlpsgame.com/guide-jdownloader-2/</v>
       </c>
     </row>
@@ -2897,27 +2478,30 @@
         <v>imagenes/PS3/Jikkyou Powerful Pro Yakyuu 2016.jpg</v>
       </c>
       <c r="E53" t="str">
-        <v>No</v>
+        <v>No disponible</v>
       </c>
       <c r="F53" t="str">
+        <v>No</v>
+      </c>
+      <c r="G53" t="str">
         <v>https://goo.gl/WLRe7r</v>
       </c>
-      <c r="K53" t="str">
-        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
-      </c>
-      <c r="W53" t="str">
+      <c r="H53" t="str">
+        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
+      </c>
+      <c r="I53" t="str">
         <v>https://1fichier.com/?x8nli6wxh6y3t0ctn1gj</v>
       </c>
-      <c r="AK53" t="str">
+      <c r="N53" t="str">
         <v>https://downloadgameps3.net/archives/10044</v>
       </c>
-      <c r="AL53" t="str">
-        <v>https://gamepciso.com/</v>
-      </c>
-      <c r="AM53" t="str">
-        <v>https://downloadgameps3.net/archives/18667</v>
-      </c>
-      <c r="AN53" t="str">
+      <c r="O53" t="str">
+        <v>https://gamepciso.com/</v>
+      </c>
+      <c r="P53" t="str">
+        <v>https://downloadgameps3.net/archives/18667</v>
+      </c>
+      <c r="Q53" t="str">
         <v>https://dlpsgame.com/guide-jdownloader-2/</v>
       </c>
     </row>
@@ -2935,27 +2519,30 @@
         <v>imagenes/PS3/Kono Oozora ni Tsubasa o Hirogete Cruise Sign.jpg</v>
       </c>
       <c r="E54" t="str">
-        <v>No</v>
+        <v>No disponible</v>
       </c>
       <c r="F54" t="str">
+        <v>No</v>
+      </c>
+      <c r="G54" t="str">
         <v>https://goo.gl/74p5P6</v>
       </c>
-      <c r="K54" t="str">
-        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
-      </c>
-      <c r="W54" t="str">
+      <c r="H54" t="str">
+        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
+      </c>
+      <c r="I54" t="str">
         <v>https://1fichier.com/?bicz35r6vthum8xie1kl</v>
       </c>
-      <c r="AK54" t="str">
+      <c r="N54" t="str">
         <v>https://downloadgameps3.net/archives/10215</v>
       </c>
-      <c r="AL54" t="str">
-        <v>https://gamepciso.com/</v>
-      </c>
-      <c r="AM54" t="str">
-        <v>https://downloadgameps3.net/archives/18667</v>
-      </c>
-      <c r="AN54" t="str">
+      <c r="O54" t="str">
+        <v>https://gamepciso.com/</v>
+      </c>
+      <c r="P54" t="str">
+        <v>https://downloadgameps3.net/archives/18667</v>
+      </c>
+      <c r="Q54" t="str">
         <v>https://dlpsgame.com/guide-jdownloader-2/</v>
       </c>
     </row>
@@ -2973,27 +2560,30 @@
         <v>imagenes/PS3/Nobunaga no Yabou Souzou Sengoku Risshiden.jpg</v>
       </c>
       <c r="E55" t="str">
-        <v>No</v>
+        <v>No disponible</v>
       </c>
       <c r="F55" t="str">
+        <v>No</v>
+      </c>
+      <c r="G55" t="str">
         <v>https://goo.gl/MJqpsc</v>
       </c>
-      <c r="K55" t="str">
-        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
-      </c>
-      <c r="W55" t="str">
+      <c r="H55" t="str">
+        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
+      </c>
+      <c r="I55" t="str">
         <v>https://1fichier.com/?azn98thbjf5ay7mk89ax</v>
       </c>
-      <c r="AK55" t="str">
+      <c r="N55" t="str">
         <v>https://downloadgameps3.net/archives/11127</v>
       </c>
-      <c r="AL55" t="str">
-        <v>https://gamepciso.com/</v>
-      </c>
-      <c r="AM55" t="str">
-        <v>https://downloadgameps3.net/archives/18667</v>
-      </c>
-      <c r="AN55" t="str">
+      <c r="O55" t="str">
+        <v>https://gamepciso.com/</v>
+      </c>
+      <c r="P55" t="str">
+        <v>https://downloadgameps3.net/archives/18667</v>
+      </c>
+      <c r="Q55" t="str">
         <v>https://dlpsgame.com/guide-jdownloader-2/</v>
       </c>
     </row>
@@ -3011,27 +2601,30 @@
         <v>imagenes/PS3/Super Robot Taisen OG The Moon Dwellers.jpg</v>
       </c>
       <c r="E56" t="str">
-        <v>No</v>
+        <v>No disponible</v>
       </c>
       <c r="F56" t="str">
+        <v>No</v>
+      </c>
+      <c r="G56" t="str">
         <v>http://bit.ly/2MHOUB2</v>
       </c>
-      <c r="K56" t="str">
-        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
-      </c>
-      <c r="W56" t="str">
+      <c r="H56" t="str">
+        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
+      </c>
+      <c r="I56" t="str">
         <v>https://1fichier.com/?2e6gd6205yjw8nbcwyau</v>
       </c>
-      <c r="AK56" t="str">
+      <c r="N56" t="str">
         <v>https://downloadgameps3.net/archives/12183</v>
       </c>
-      <c r="AL56" t="str">
-        <v>https://gamepciso.com/</v>
-      </c>
-      <c r="AM56" t="str">
-        <v>https://downloadgameps3.net/archives/18667</v>
-      </c>
-      <c r="AN56" t="str">
+      <c r="O56" t="str">
+        <v>https://gamepciso.com/</v>
+      </c>
+      <c r="P56" t="str">
+        <v>https://downloadgameps3.net/archives/18667</v>
+      </c>
+      <c r="Q56" t="str">
         <v>https://dlpsgame.com/guide-jdownloader-2/</v>
       </c>
     </row>
@@ -3049,30 +2642,33 @@
         <v>imagenes/PS3/Stormrise.jpg</v>
       </c>
       <c r="E57" t="str">
-        <v>No</v>
+        <v>No disponible</v>
       </c>
       <c r="F57" t="str">
+        <v>No</v>
+      </c>
+      <c r="G57" t="str">
         <v>https://filecrypt.cc/Container/CBA7D16250.html</v>
       </c>
-      <c r="K57" t="str">
-        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
-      </c>
-      <c r="W57" t="str">
+      <c r="H57" t="str">
+        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
+      </c>
+      <c r="I57" t="str">
         <v>https://1fichier.com/?tgfskf3xca6fdcpqojov</v>
       </c>
-      <c r="AK57" t="str">
+      <c r="N57" t="str">
         <v>https://downloadgameps3.net/archives/12149</v>
       </c>
-      <c r="AL57" t="str">
+      <c r="O57" t="str">
         <v>https://downloadgameps3.net/archives/12147</v>
       </c>
-      <c r="AM57" t="str">
-        <v>https://gamepciso.com/</v>
-      </c>
-      <c r="AN57" t="str">
-        <v>https://downloadgameps3.net/archives/18667</v>
-      </c>
-      <c r="AO57" t="str">
+      <c r="P57" t="str">
+        <v>https://gamepciso.com/</v>
+      </c>
+      <c r="Q57" t="str">
+        <v>https://downloadgameps3.net/archives/18667</v>
+      </c>
+      <c r="R57" t="str">
         <v>https://dlpsgame.com/guide-jdownloader-2/</v>
       </c>
     </row>
@@ -3090,42 +2686,24 @@
         <v>imagenes/PS3/Pro Evolution Soccer 2016 [PES 2016].jpg</v>
       </c>
       <c r="E58" t="str">
-        <v>No</v>
-      </c>
-      <c r="G58" t="str">
-        <v>http://bit.ly/2UAEu62</v>
-      </c>
-      <c r="H58" t="str">
-        <v>https://filecrypt.cc/Container/1C98D8396C.html</v>
-      </c>
-      <c r="L58" t="str">
-        <v>https://filecrypt.cc/Container/004FCFDDE1.html</v>
-      </c>
-      <c r="M58" t="str">
-        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
-      </c>
-      <c r="X58" t="str">
-        <v>https://1fichier.com/?re4d05urgrek6lrwq4h0</v>
-      </c>
-      <c r="Y58" t="str">
-        <v>https://1fichier.com/?osi3ngfoi0n9tofj0ml8</v>
-      </c>
-      <c r="Z58" t="str">
-        <v>https://1fichier.com/?oagch1rhsprq50o4sk4z</v>
-      </c>
-      <c r="AK58" t="str">
+        <v>No disponible</v>
+      </c>
+      <c r="F58" t="str">
+        <v>No</v>
+      </c>
+      <c r="N58" t="str">
         <v>https://downloadgameps3.net/archives/11242</v>
       </c>
-      <c r="AL58" t="str">
+      <c r="O58" t="str">
         <v>https://downloadgameps3.net/archives/11244</v>
       </c>
-      <c r="AM58" t="str">
-        <v>https://gamepciso.com/</v>
-      </c>
-      <c r="AN58" t="str">
-        <v>https://downloadgameps3.net/archives/18667</v>
-      </c>
-      <c r="AO58" t="str">
+      <c r="P58" t="str">
+        <v>https://gamepciso.com/</v>
+      </c>
+      <c r="Q58" t="str">
+        <v>https://downloadgameps3.net/archives/18667</v>
+      </c>
+      <c r="R58" t="str">
         <v>https://dlpsgame.com/guide-jdownloader-2/</v>
       </c>
     </row>
@@ -3143,42 +2721,30 @@
         <v>imagenes/PS3/FIFA 16.jpg</v>
       </c>
       <c r="E59" t="str">
-        <v>No</v>
+        <v>No disponible</v>
       </c>
       <c r="F59" t="str">
+        <v>No</v>
+      </c>
+      <c r="G59" t="str">
         <v>https://filecrypt.cc/Container/F2BA21EF11.html</v>
       </c>
-      <c r="L59" t="str">
-        <v>https://filecrypt.cc/Container/AE9D5CF725.html</v>
-      </c>
-      <c r="M59" t="str">
-        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
-      </c>
-      <c r="X59" t="str">
-        <v>https://1fichier.com/?gaxd3zgr64nsuo6fac4r</v>
-      </c>
-      <c r="Y59" t="str">
-        <v>https://1fichier.com/?45h9tf0d88r9q252qlh9</v>
-      </c>
-      <c r="Z59" t="str">
-        <v>https://1fichier.com/?55dlvnzrz7r02nrp21et</v>
-      </c>
-      <c r="AK59" t="str">
+      <c r="N59" t="str">
         <v>https://downloadgameps3.net/archives/9374</v>
       </c>
-      <c r="AL59" t="str">
+      <c r="O59" t="str">
         <v>https://downloadgameps3.net/archives/9370</v>
       </c>
-      <c r="AM59" t="str">
+      <c r="P59" t="str">
         <v>https://downloadgameps3.net/archives/9372</v>
       </c>
-      <c r="AN59" t="str">
-        <v>https://gamepciso.com/</v>
-      </c>
-      <c r="AO59" t="str">
-        <v>https://downloadgameps3.net/archives/18667</v>
-      </c>
-      <c r="AP59" t="str">
+      <c r="Q59" t="str">
+        <v>https://gamepciso.com/</v>
+      </c>
+      <c r="R59" t="str">
+        <v>https://downloadgameps3.net/archives/18667</v>
+      </c>
+      <c r="S59" t="str">
         <v>https://dlpsgame.com/guide-jdownloader-2/</v>
       </c>
     </row>
@@ -3196,36 +2762,33 @@
         <v>imagenes/PS3/Toukiden 2.jpg</v>
       </c>
       <c r="E60" t="str">
-        <v>No</v>
+        <v>No disponible</v>
       </c>
       <c r="F60" t="str">
+        <v>No</v>
+      </c>
+      <c r="G60" t="str">
         <v>https://filecrypt.cc/Container/FF76F61FC7.html</v>
       </c>
-      <c r="K60" t="str">
-        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
-      </c>
-      <c r="X60" t="str">
-        <v>https://1fichier.com/?al9o4vodl4t1irae5flb</v>
-      </c>
-      <c r="Y60" t="str">
-        <v>https://1fichier.com/?hyu8ratckhxgq60oysz1</v>
-      </c>
-      <c r="AK60" t="str">
+      <c r="H60" t="str">
+        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
+      </c>
+      <c r="N60" t="str">
         <v>https://downloadgameps3.net/archives/12480</v>
       </c>
-      <c r="AL60" t="str">
+      <c r="O60" t="str">
         <v>http://b0.ww.np.dl.playstation.net/tppkg/np/BLJM61344/BLJM61344_T5/01a99e846a26fdac/JP0106-BLJM61344_00-TOUKIDEN20000000-A0106-V0100-PE.pkg</v>
       </c>
-      <c r="AM60" t="str">
+      <c r="P60" t="str">
         <v>https://filecrypt.cc/Container/60F90DF209.html</v>
       </c>
-      <c r="AN60" t="str">
-        <v>https://gamepciso.com/</v>
-      </c>
-      <c r="AO60" t="str">
-        <v>https://downloadgameps3.net/archives/18667</v>
-      </c>
-      <c r="AP60" t="str">
+      <c r="Q60" t="str">
+        <v>https://gamepciso.com/</v>
+      </c>
+      <c r="R60" t="str">
+        <v>https://downloadgameps3.net/archives/18667</v>
+      </c>
+      <c r="S60" t="str">
         <v>https://dlpsgame.com/guide-jdownloader-2/</v>
       </c>
     </row>
@@ -3243,27 +2806,30 @@
         <v>imagenes/PS3/Utawarerumono Futari no Hakuoro.jpg</v>
       </c>
       <c r="E61" t="str">
-        <v>No</v>
-      </c>
-      <c r="K61" t="str">
-        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
-      </c>
-      <c r="AK61" t="str">
+        <v>No disponible</v>
+      </c>
+      <c r="F61" t="str">
+        <v>No</v>
+      </c>
+      <c r="H61" t="str">
+        <v>https://dlpsgame.com/guide-to-download-at-highest-speed/</v>
+      </c>
+      <c r="N61" t="str">
         <v>https://downloadgameps3.net/archives/12640</v>
       </c>
-      <c r="AL61" t="str">
-        <v>https://gamepciso.com/</v>
-      </c>
-      <c r="AM61" t="str">
-        <v>https://downloadgameps3.net/archives/18667</v>
-      </c>
-      <c r="AN61" t="str">
+      <c r="O61" t="str">
+        <v>https://gamepciso.com/</v>
+      </c>
+      <c r="P61" t="str">
+        <v>https://downloadgameps3.net/archives/18667</v>
+      </c>
+      <c r="Q61" t="str">
         <v>https://dlpsgame.com/guide-jdownloader-2/</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AU61"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:X61"/>
   </ignoredErrors>
 </worksheet>
 </file>